--- a/research/traditional_assets/database/data/slovenia/slovenia_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/slovenia/slovenia_hotel_gaming.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="ljse_shbr" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -587,116 +589,95 @@
           <t>Hotel/Gaming</t>
         </is>
       </c>
-      <c r="D2">
-        <v>-0.118</v>
-      </c>
       <c r="G2">
-        <v>0.2194444444444444</v>
+        <v>0.2114035087719298</v>
       </c>
       <c r="H2">
-        <v>0.2194444444444444</v>
+        <v>0.2114035087719298</v>
       </c>
       <c r="I2">
-        <v>-0.04439814814814814</v>
+        <v>0.1052631578947368</v>
       </c>
       <c r="J2">
-        <v>-0.04439814814814814</v>
+        <v>0.09569377990430621</v>
       </c>
       <c r="K2">
-        <v>6.44</v>
+        <v>13</v>
       </c>
       <c r="L2">
-        <v>0.2981481481481482</v>
+        <v>0.1140350877192982</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.02285407725321888</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.1638461538461538</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.02285407725321888</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.1638461538461538</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>0.1741379310344828</v>
-      </c>
-      <c r="W2">
-        <v>0.06729362591431558</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>0.2239058524873587</v>
-      </c>
-      <c r="Y2">
-        <v>-0.1566122265730431</v>
-      </c>
-      <c r="Z2">
-        <v>0.1462819991873222</v>
-      </c>
-      <c r="AA2">
-        <v>-0.006494649871326019</v>
+        <v>0.08632573372503716</v>
       </c>
       <c r="AB2">
-        <v>0.09863314327915851</v>
-      </c>
-      <c r="AC2">
-        <v>-0.1051277931504845</v>
+        <v>0.08632573372503716</v>
       </c>
       <c r="AD2">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>41.97</v>
+        <v>0</v>
       </c>
       <c r="AH2">
-        <v>0.7211538461538461</v>
-      </c>
-      <c r="AI2">
-        <v>0.2858958068614993</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>0.7069226882263769</v>
-      </c>
-      <c r="AK2">
-        <v>0.2718792511498348</v>
+        <v>0</v>
       </c>
       <c r="AL2">
-        <v>2.35</v>
+        <v>1.49</v>
       </c>
       <c r="AM2">
-        <v>-6.67</v>
+        <v>1.331</v>
       </c>
       <c r="AN2">
-        <v>11.22194513715711</v>
+        <v>0</v>
       </c>
       <c r="AO2">
-        <v>-0.4080851063829787</v>
+        <v>8.053691275167786</v>
       </c>
       <c r="AP2">
-        <v>10.46633416458853</v>
+        <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0.1437781109445277</v>
+        <v>9.015777610818933</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +688,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Terme Catez, d.d. (LJSE:TCRG)</t>
+          <t>Sava Turizem d.d. (LJSE:SHBR)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -715,116 +696,8864 @@
           <t>Hotel/Gaming</t>
         </is>
       </c>
+      <c r="G3">
+        <v>0.2114035087719298</v>
+      </c>
+      <c r="H3">
+        <v>0.2114035087719298</v>
+      </c>
+      <c r="I3">
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="J3">
+        <v>0.09569377990430621</v>
+      </c>
+      <c r="K3">
+        <v>13</v>
+      </c>
+      <c r="L3">
+        <v>0.1140350877192982</v>
+      </c>
+      <c r="M3">
+        <v>2.13</v>
+      </c>
+      <c r="N3">
+        <v>0.02285407725321888</v>
+      </c>
+      <c r="O3">
+        <v>0.1638461538461538</v>
+      </c>
+      <c r="P3">
+        <v>2.13</v>
+      </c>
+      <c r="Q3">
+        <v>0.02285407725321888</v>
+      </c>
+      <c r="R3">
+        <v>0.1638461538461538</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0.08632573372503716</v>
+      </c>
+      <c r="AB3">
+        <v>0.08632573372503716</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>1.49</v>
+      </c>
+      <c r="AM3">
+        <v>1.331</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>8.053691275167786</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>9.015777610818933</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sava Turizem d.d. (LJSE:SHBR)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LJSE:SHBR</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Hotel/Gaming</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>7.58389261744967</v>
+      </c>
+      <c r="F2">
+        <v>4.58080078559517</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>2.01095435684647</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.52</v>
+      </c>
+      <c r="K2">
+        <v>93.2</v>
+      </c>
+      <c r="L2">
+        <v>47.266496296301</v>
+      </c>
+      <c r="M2">
+        <v>93.2</v>
+      </c>
+      <c r="N2">
+        <v>95.730496296301</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>48.464</v>
+      </c>
+      <c r="Q2">
+        <v>0.0863257337250372</v>
+      </c>
+      <c r="R2">
+        <v>0.0828932712330035</v>
+      </c>
+      <c r="S2">
+        <v>0.0470638808926358</v>
+      </c>
+      <c r="T2">
+        <v>0.041229</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.0863257337250372</v>
+      </c>
+      <c r="X2">
+        <v>0.128029565068757</v>
+      </c>
+      <c r="Y2">
+        <v>0.7480479046815171</v>
+      </c>
+      <c r="Z2">
+        <v>1.40445994103955</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0.05810355665757501</v>
+      </c>
+      <c r="AC2">
+        <v>7.583892617449665</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>1.49</v>
+      </c>
+      <c r="AF2">
+        <v>12.8</v>
+      </c>
+      <c r="AG2">
+        <v>24.1</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>93.2</v>
+      </c>
+      <c r="AK2">
+        <v>0.06353300828410362</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.19</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AR2">
+        <v>1.49</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.08632573372503716</v>
+      </c>
+      <c r="C2">
+        <v>93.2</v>
+      </c>
+      <c r="D2">
+        <v>93.2</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>93.2</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>24.1</v>
+      </c>
+      <c r="K2">
+        <v>12.8</v>
+      </c>
+      <c r="L2">
+        <v>11.3</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>11.3</v>
+      </c>
+      <c r="O2">
+        <v>2.147</v>
+      </c>
+      <c r="P2">
+        <v>9.153</v>
+      </c>
+      <c r="Q2">
+        <v>21.953</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.08632573372503716</v>
+      </c>
+      <c r="T2">
+        <v>0.7480479046815168</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.19</v>
+      </c>
+      <c r="W2">
+        <v>0.036207</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.0862095048309596</v>
+      </c>
+      <c r="C3">
+        <v>92.35149654731319</v>
+      </c>
       <c r="D3">
-        <v>-0.118</v>
+        <v>93.28349654731319</v>
+      </c>
+      <c r="E3">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="F3">
+        <v>0.9320000000000001</v>
       </c>
       <c r="G3">
-        <v>0.2194444444444444</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.2194444444444444</v>
+        <v>93.2</v>
       </c>
       <c r="I3">
-        <v>-0.04439814814814814</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>-0.04439814814814814</v>
+        <v>24.1</v>
       </c>
       <c r="K3">
-        <v>6.44</v>
+        <v>12.8</v>
       </c>
       <c r="L3">
-        <v>0.2981481481481482</v>
+        <v>11.3</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.04166040000000001</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>11.2583396</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>2.139084524</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>9.119255076000002</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>21.919255076</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.08671458063733292</v>
+      </c>
+      <c r="T3">
+        <v>0.7541682966289112</v>
       </c>
       <c r="U3">
-        <v>3.03</v>
+        <v>0.0447</v>
       </c>
       <c r="V3">
-        <v>0.1741379310344828</v>
+        <v>0.19</v>
       </c>
       <c r="W3">
-        <v>0.06729362591431558</v>
-      </c>
-      <c r="X3">
-        <v>0.2239058524873587</v>
+        <v>0.036207</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
       </c>
       <c r="Y3">
-        <v>-0.1566122265730431</v>
+        <v>271.2407946155101</v>
       </c>
       <c r="Z3">
-        <v>0.1462819991873222</v>
-      </c>
-      <c r="AA3">
-        <v>-0.006494649871326019</v>
-      </c>
-      <c r="AB3">
-        <v>0.09863314327915851</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1051277931504845</v>
-      </c>
-      <c r="AD3">
-        <v>45</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>45</v>
-      </c>
-      <c r="AG3">
-        <v>41.97</v>
-      </c>
-      <c r="AH3">
-        <v>0.7211538461538461</v>
-      </c>
-      <c r="AI3">
-        <v>0.2858958068614993</v>
-      </c>
-      <c r="AJ3">
-        <v>0.7069226882263769</v>
-      </c>
-      <c r="AK3">
-        <v>0.2718792511498348</v>
-      </c>
-      <c r="AL3">
-        <v>2.35</v>
-      </c>
-      <c r="AM3">
-        <v>-6.67</v>
-      </c>
-      <c r="AN3">
-        <v>11.22194513715711</v>
-      </c>
-      <c r="AO3">
-        <v>-0.4080851063829787</v>
-      </c>
-      <c r="AP3">
-        <v>10.46633416458853</v>
-      </c>
-      <c r="AQ3">
-        <v>0.1437781109445277</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.08609327593688203</v>
+      </c>
+      <c r="C4">
+        <v>91.50314283550271</v>
+      </c>
+      <c r="D4">
+        <v>93.36714283550272</v>
+      </c>
+      <c r="E4">
+        <v>1.864</v>
+      </c>
+      <c r="F4">
+        <v>1.864</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>93.2</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>24.1</v>
+      </c>
+      <c r="K4">
+        <v>12.8</v>
+      </c>
+      <c r="L4">
+        <v>11.3</v>
+      </c>
+      <c r="M4">
+        <v>0.08332080000000001</v>
+      </c>
+      <c r="N4">
+        <v>11.2166792</v>
+      </c>
+      <c r="O4">
+        <v>2.131169048</v>
+      </c>
+      <c r="P4">
+        <v>9.085510152000001</v>
+      </c>
+      <c r="Q4">
+        <v>21.885510152</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08711136320090003</v>
+      </c>
+      <c r="T4">
+        <v>0.7604135945344155</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.19</v>
+      </c>
+      <c r="W4">
+        <v>0.036207</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>135.6203973077551</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.08597704704280446</v>
+      </c>
+      <c r="C5">
+        <v>90.65493926774307</v>
+      </c>
+      <c r="D5">
+        <v>93.45093926774308</v>
+      </c>
+      <c r="E5">
+        <v>2.796</v>
+      </c>
+      <c r="F5">
+        <v>2.796</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>93.2</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>24.1</v>
+      </c>
+      <c r="K5">
+        <v>12.8</v>
+      </c>
+      <c r="L5">
+        <v>11.3</v>
+      </c>
+      <c r="M5">
+        <v>0.1249812</v>
+      </c>
+      <c r="N5">
+        <v>11.1750188</v>
+      </c>
+      <c r="O5">
+        <v>2.123253572</v>
+      </c>
+      <c r="P5">
+        <v>9.051765228000001</v>
+      </c>
+      <c r="Q5">
+        <v>21.851765228</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.08751632684825202</v>
+      </c>
+      <c r="T5">
+        <v>0.7667876614688992</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.19</v>
+      </c>
+      <c r="W5">
+        <v>0.036207</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>90.41359820517006</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.08586081814872687</v>
+      </c>
+      <c r="C6">
+        <v>89.80688624865751</v>
+      </c>
+      <c r="D6">
+        <v>93.5348862486575</v>
+      </c>
+      <c r="E6">
+        <v>3.728</v>
+      </c>
+      <c r="F6">
+        <v>3.728</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>93.2</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>24.1</v>
+      </c>
+      <c r="K6">
+        <v>12.8</v>
+      </c>
+      <c r="L6">
+        <v>11.3</v>
+      </c>
+      <c r="M6">
+        <v>0.1666416</v>
+      </c>
+      <c r="N6">
+        <v>11.1333584</v>
+      </c>
+      <c r="O6">
+        <v>2.115338096</v>
+      </c>
+      <c r="P6">
+        <v>9.018020304</v>
+      </c>
+      <c r="Q6">
+        <v>21.818020304</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.08792972723825716</v>
+      </c>
+      <c r="T6">
+        <v>0.7732945214645179</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.19</v>
+      </c>
+      <c r="W6">
+        <v>0.036207</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>67.81019865387753</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.0857445892546493</v>
+      </c>
+      <c r="C7">
+        <v>88.95898418432438</v>
+      </c>
+      <c r="D7">
+        <v>93.61898418432438</v>
+      </c>
+      <c r="E7">
+        <v>4.66</v>
+      </c>
+      <c r="F7">
+        <v>4.66</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>93.2</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>24.1</v>
+      </c>
+      <c r="K7">
+        <v>12.8</v>
+      </c>
+      <c r="L7">
+        <v>11.3</v>
+      </c>
+      <c r="M7">
+        <v>0.208302</v>
+      </c>
+      <c r="N7">
+        <v>11.091698</v>
+      </c>
+      <c r="O7">
+        <v>2.10742262</v>
+      </c>
+      <c r="P7">
+        <v>8.98427538</v>
+      </c>
+      <c r="Q7">
+        <v>21.78427538</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.08835183079436769</v>
+      </c>
+      <c r="T7">
+        <v>0.7799383679863604</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.19</v>
+      </c>
+      <c r="W7">
+        <v>0.036207</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>54.24815892310203</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.08562836036057173</v>
+      </c>
+      <c r="C8">
+        <v>88.11123348228391</v>
+      </c>
+      <c r="D8">
+        <v>93.70323348228391</v>
+      </c>
+      <c r="E8">
+        <v>5.592</v>
+      </c>
+      <c r="F8">
+        <v>5.592</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>93.2</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>24.1</v>
+      </c>
+      <c r="K8">
+        <v>12.8</v>
+      </c>
+      <c r="L8">
+        <v>11.3</v>
+      </c>
+      <c r="M8">
+        <v>0.2499624</v>
+      </c>
+      <c r="N8">
+        <v>11.0500376</v>
+      </c>
+      <c r="O8">
+        <v>2.099507144</v>
+      </c>
+      <c r="P8">
+        <v>8.950530456000001</v>
+      </c>
+      <c r="Q8">
+        <v>21.750530456</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.08878291527720397</v>
+      </c>
+      <c r="T8">
+        <v>0.7867235729448377</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.19</v>
+      </c>
+      <c r="W8">
+        <v>0.036207</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>45.20679910258503</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.08551213146649417</v>
+      </c>
+      <c r="C9">
+        <v>87.2636345515445</v>
+      </c>
+      <c r="D9">
+        <v>93.7876345515445</v>
+      </c>
+      <c r="E9">
+        <v>6.524000000000001</v>
+      </c>
+      <c r="F9">
+        <v>6.524000000000001</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>93.2</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>24.1</v>
+      </c>
+      <c r="K9">
+        <v>12.8</v>
+      </c>
+      <c r="L9">
+        <v>11.3</v>
+      </c>
+      <c r="M9">
+        <v>0.2916228000000001</v>
+      </c>
+      <c r="N9">
+        <v>11.0083772</v>
+      </c>
+      <c r="O9">
+        <v>2.091591668</v>
+      </c>
+      <c r="P9">
+        <v>8.916785532</v>
+      </c>
+      <c r="Q9">
+        <v>21.716785532</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.08922327039407976</v>
+      </c>
+      <c r="T9">
+        <v>0.793654696289519</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.19</v>
+      </c>
+      <c r="W9">
+        <v>0.036207</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>38.74868494507287</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.08539590257241662</v>
+      </c>
+      <c r="C10">
+        <v>86.41618780258968</v>
+      </c>
+      <c r="D10">
+        <v>93.87218780258968</v>
+      </c>
+      <c r="E10">
+        <v>7.456</v>
+      </c>
+      <c r="F10">
+        <v>7.456</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>93.2</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>24.1</v>
+      </c>
+      <c r="K10">
+        <v>12.8</v>
+      </c>
+      <c r="L10">
+        <v>11.3</v>
+      </c>
+      <c r="M10">
+        <v>0.3332832000000001</v>
+      </c>
+      <c r="N10">
+        <v>10.9667168</v>
+      </c>
+      <c r="O10">
+        <v>2.083676192</v>
+      </c>
+      <c r="P10">
+        <v>8.883040608</v>
+      </c>
+      <c r="Q10">
+        <v>21.683040608</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.08967319844827892</v>
+      </c>
+      <c r="T10">
+        <v>0.8007364962286498</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.19</v>
+      </c>
+      <c r="W10">
+        <v>0.036207</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>33.90509932693877</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.08527967367833902</v>
+      </c>
+      <c r="C11">
+        <v>85.56889364738447</v>
+      </c>
+      <c r="D11">
+        <v>93.95689364738448</v>
+      </c>
+      <c r="E11">
+        <v>8.388</v>
+      </c>
+      <c r="F11">
+        <v>8.388</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>93.2</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>24.1</v>
+      </c>
+      <c r="K11">
+        <v>12.8</v>
+      </c>
+      <c r="L11">
+        <v>11.3</v>
+      </c>
+      <c r="M11">
+        <v>0.3749436</v>
+      </c>
+      <c r="N11">
+        <v>10.9250564</v>
+      </c>
+      <c r="O11">
+        <v>2.075760716</v>
+      </c>
+      <c r="P11">
+        <v>8.849295684000001</v>
+      </c>
+      <c r="Q11">
+        <v>21.649295684</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.09013301503114178</v>
+      </c>
+      <c r="T11">
+        <v>0.8079739401224866</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.19</v>
+      </c>
+      <c r="W11">
+        <v>0.036207</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>30.13786606839002</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.08516344478426147</v>
+      </c>
+      <c r="C12">
+        <v>84.72175249938218</v>
+      </c>
+      <c r="D12">
+        <v>94.04175249938218</v>
+      </c>
+      <c r="E12">
+        <v>9.32</v>
+      </c>
+      <c r="F12">
+        <v>9.32</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>93.2</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>24.1</v>
+      </c>
+      <c r="K12">
+        <v>12.8</v>
+      </c>
+      <c r="L12">
+        <v>11.3</v>
+      </c>
+      <c r="M12">
+        <v>0.416604</v>
+      </c>
+      <c r="N12">
+        <v>10.883396</v>
+      </c>
+      <c r="O12">
+        <v>2.06784524</v>
+      </c>
+      <c r="P12">
+        <v>8.815550760000001</v>
+      </c>
+      <c r="Q12">
+        <v>21.61555076</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.09060304976029052</v>
+      </c>
+      <c r="T12">
+        <v>0.8153722161028534</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.19</v>
+      </c>
+      <c r="W12">
+        <v>0.036207</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>27.12407946155102</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.08504721589018388</v>
+      </c>
+      <c r="C13">
+        <v>83.87476477353123</v>
+      </c>
+      <c r="D13">
+        <v>94.12676477353122</v>
+      </c>
+      <c r="E13">
+        <v>10.252</v>
+      </c>
+      <c r="F13">
+        <v>10.252</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>93.2</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>24.1</v>
+      </c>
+      <c r="K13">
+        <v>12.8</v>
+      </c>
+      <c r="L13">
+        <v>11.3</v>
+      </c>
+      <c r="M13">
+        <v>0.4582644000000001</v>
+      </c>
+      <c r="N13">
+        <v>10.8417356</v>
+      </c>
+      <c r="O13">
+        <v>2.059929764</v>
+      </c>
+      <c r="P13">
+        <v>8.781805836</v>
+      </c>
+      <c r="Q13">
+        <v>21.581805836</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.09108364706762234</v>
+      </c>
+      <c r="T13">
+        <v>0.8229367454760372</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.19</v>
+      </c>
+      <c r="W13">
+        <v>0.036207</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>24.65825405595547</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.08493098699610632</v>
+      </c>
+      <c r="C14">
+        <v>83.02793088628165</v>
+      </c>
+      <c r="D14">
+        <v>94.21193088628165</v>
+      </c>
+      <c r="E14">
+        <v>11.184</v>
+      </c>
+      <c r="F14">
+        <v>11.184</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>93.2</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>24.1</v>
+      </c>
+      <c r="K14">
+        <v>12.8</v>
+      </c>
+      <c r="L14">
+        <v>11.3</v>
+      </c>
+      <c r="M14">
+        <v>0.4999248</v>
+      </c>
+      <c r="N14">
+        <v>10.8000752</v>
+      </c>
+      <c r="O14">
+        <v>2.052014288</v>
+      </c>
+      <c r="P14">
+        <v>8.748060912</v>
+      </c>
+      <c r="Q14">
+        <v>21.548060912</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.0915751670410299</v>
+      </c>
+      <c r="T14">
+        <v>0.8306731959713388</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.19</v>
+      </c>
+      <c r="W14">
+        <v>0.036207</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>22.60339955129252</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.08481475810202874</v>
+      </c>
+      <c r="C15">
+        <v>82.18125125559229</v>
+      </c>
+      <c r="D15">
+        <v>94.29725125559229</v>
+      </c>
+      <c r="E15">
+        <v>12.116</v>
+      </c>
+      <c r="F15">
+        <v>12.116</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>93.2</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>24.1</v>
+      </c>
+      <c r="K15">
+        <v>12.8</v>
+      </c>
+      <c r="L15">
+        <v>11.3</v>
+      </c>
+      <c r="M15">
+        <v>0.5415852000000001</v>
+      </c>
+      <c r="N15">
+        <v>10.7584148</v>
+      </c>
+      <c r="O15">
+        <v>2.044098812</v>
+      </c>
+      <c r="P15">
+        <v>8.714315988000001</v>
+      </c>
+      <c r="Q15">
+        <v>21.514315988</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.09207798632417097</v>
+      </c>
+      <c r="T15">
+        <v>0.8385874959033143</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.19</v>
+      </c>
+      <c r="W15">
+        <v>0.036207</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>20.8646765088854</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.08469852920795118</v>
+      </c>
+      <c r="C16">
+        <v>81.33472630093721</v>
+      </c>
+      <c r="D16">
+        <v>94.38272630093721</v>
+      </c>
+      <c r="E16">
+        <v>13.048</v>
+      </c>
+      <c r="F16">
+        <v>13.048</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>93.2</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>24.1</v>
+      </c>
+      <c r="K16">
+        <v>12.8</v>
+      </c>
+      <c r="L16">
+        <v>11.3</v>
+      </c>
+      <c r="M16">
+        <v>0.5832456000000001</v>
+      </c>
+      <c r="N16">
+        <v>10.7167544</v>
+      </c>
+      <c r="O16">
+        <v>2.036183336</v>
+      </c>
+      <c r="P16">
+        <v>8.680571064</v>
+      </c>
+      <c r="Q16">
+        <v>21.480571064</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.092592499079013</v>
+      </c>
+      <c r="T16">
+        <v>0.8466858493220797</v>
+      </c>
+      <c r="U16">
+        <v>0.0447</v>
+      </c>
+      <c r="V16">
+        <v>0.19</v>
+      </c>
+      <c r="W16">
+        <v>0.036207</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>19.37434247253644</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.08458230031387361</v>
+      </c>
+      <c r="C17">
+        <v>80.48835644331291</v>
+      </c>
+      <c r="D17">
+        <v>94.46835644331291</v>
+      </c>
+      <c r="E17">
+        <v>13.98</v>
+      </c>
+      <c r="F17">
+        <v>13.98</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>93.2</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>24.1</v>
+      </c>
+      <c r="K17">
+        <v>12.8</v>
+      </c>
+      <c r="L17">
+        <v>11.3</v>
+      </c>
+      <c r="M17">
+        <v>0.6249060000000001</v>
+      </c>
+      <c r="N17">
+        <v>10.675094</v>
+      </c>
+      <c r="O17">
+        <v>2.02826786</v>
+      </c>
+      <c r="P17">
+        <v>8.646826140000002</v>
+      </c>
+      <c r="Q17">
+        <v>21.44682614</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.09311911801632189</v>
+      </c>
+      <c r="T17">
+        <v>0.8549747522330514</v>
+      </c>
+      <c r="U17">
+        <v>0.0447</v>
+      </c>
+      <c r="V17">
+        <v>0.19</v>
+      </c>
+      <c r="W17">
+        <v>0.036207</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>18.08271964103401</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.08446607141979603</v>
+      </c>
+      <c r="C18">
+        <v>79.64214210524503</v>
+      </c>
+      <c r="D18">
+        <v>94.55414210524503</v>
+      </c>
+      <c r="E18">
+        <v>14.912</v>
+      </c>
+      <c r="F18">
+        <v>14.912</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>93.2</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>24.1</v>
+      </c>
+      <c r="K18">
+        <v>12.8</v>
+      </c>
+      <c r="L18">
+        <v>11.3</v>
+      </c>
+      <c r="M18">
+        <v>0.6665664000000001</v>
+      </c>
+      <c r="N18">
+        <v>10.6334336</v>
+      </c>
+      <c r="O18">
+        <v>2.020352384</v>
+      </c>
+      <c r="P18">
+        <v>8.613081215999999</v>
+      </c>
+      <c r="Q18">
+        <v>21.413081216</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.09365827549975719</v>
+      </c>
+      <c r="T18">
+        <v>0.8634610099752367</v>
+      </c>
+      <c r="U18">
+        <v>0.0447</v>
+      </c>
+      <c r="V18">
+        <v>0.19</v>
+      </c>
+      <c r="W18">
+        <v>0.036207</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>16.95254966346938</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.08434984252571846</v>
+      </c>
+      <c r="C19">
+        <v>78.79608371079541</v>
+      </c>
+      <c r="D19">
+        <v>94.64008371079541</v>
+      </c>
+      <c r="E19">
+        <v>15.844</v>
+      </c>
+      <c r="F19">
+        <v>15.844</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>93.2</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>24.1</v>
+      </c>
+      <c r="K19">
+        <v>12.8</v>
+      </c>
+      <c r="L19">
+        <v>11.3</v>
+      </c>
+      <c r="M19">
+        <v>0.7082268000000002</v>
+      </c>
+      <c r="N19">
+        <v>10.5917732</v>
+      </c>
+      <c r="O19">
+        <v>2.012436908</v>
+      </c>
+      <c r="P19">
+        <v>8.579336292000001</v>
+      </c>
+      <c r="Q19">
+        <v>21.379336292</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.09421042472978128</v>
+      </c>
+      <c r="T19">
+        <v>0.8721517558557879</v>
+      </c>
+      <c r="U19">
+        <v>0.0447</v>
+      </c>
+      <c r="V19">
+        <v>0.19</v>
+      </c>
+      <c r="W19">
+        <v>0.036207</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>15.95534085973589</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.08423361363164089</v>
+      </c>
+      <c r="C20">
+        <v>77.95018168556898</v>
+      </c>
+      <c r="D20">
+        <v>94.72618168556897</v>
+      </c>
+      <c r="E20">
+        <v>16.776</v>
+      </c>
+      <c r="F20">
+        <v>16.776</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>93.2</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>24.1</v>
+      </c>
+      <c r="K20">
+        <v>12.8</v>
+      </c>
+      <c r="L20">
+        <v>11.3</v>
+      </c>
+      <c r="M20">
+        <v>0.7498872000000001</v>
+      </c>
+      <c r="N20">
+        <v>10.5501128</v>
+      </c>
+      <c r="O20">
+        <v>2.004521432</v>
+      </c>
+      <c r="P20">
+        <v>8.545591368</v>
+      </c>
+      <c r="Q20">
+        <v>21.345591368</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.09477604101419621</v>
+      </c>
+      <c r="T20">
+        <v>0.8810544711480597</v>
+      </c>
+      <c r="U20">
+        <v>0.0447</v>
+      </c>
+      <c r="V20">
+        <v>0.19</v>
+      </c>
+      <c r="W20">
+        <v>0.036207</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>15.06893303419501</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.08411738473756333</v>
+      </c>
+      <c r="C21">
+        <v>77.10443645672085</v>
+      </c>
+      <c r="D21">
+        <v>94.81243645672085</v>
+      </c>
+      <c r="E21">
+        <v>17.708</v>
+      </c>
+      <c r="F21">
+        <v>17.708</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>93.2</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>24.1</v>
+      </c>
+      <c r="K21">
+        <v>12.8</v>
+      </c>
+      <c r="L21">
+        <v>11.3</v>
+      </c>
+      <c r="M21">
+        <v>0.7915476000000001</v>
+      </c>
+      <c r="N21">
+        <v>10.5084524</v>
+      </c>
+      <c r="O21">
+        <v>1.996605956</v>
+      </c>
+      <c r="P21">
+        <v>8.511846444000001</v>
+      </c>
+      <c r="Q21">
+        <v>21.311846444</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.09535562313279422</v>
+      </c>
+      <c r="T21">
+        <v>0.890177006571005</v>
+      </c>
+      <c r="U21">
+        <v>0.0447</v>
+      </c>
+      <c r="V21">
+        <v>0.19</v>
+      </c>
+      <c r="W21">
+        <v>0.036207</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>14.27583129555317</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.08400115584348576</v>
+      </c>
+      <c r="C22">
+        <v>76.25884845296346</v>
+      </c>
+      <c r="D22">
+        <v>94.89884845296346</v>
+      </c>
+      <c r="E22">
+        <v>18.64</v>
+      </c>
+      <c r="F22">
+        <v>18.64</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>93.2</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>24.1</v>
+      </c>
+      <c r="K22">
+        <v>12.8</v>
+      </c>
+      <c r="L22">
+        <v>11.3</v>
+      </c>
+      <c r="M22">
+        <v>0.8332080000000001</v>
+      </c>
+      <c r="N22">
+        <v>10.466792</v>
+      </c>
+      <c r="O22">
+        <v>1.98869048</v>
+      </c>
+      <c r="P22">
+        <v>8.478101519999999</v>
+      </c>
+      <c r="Q22">
+        <v>21.27810152</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.09594969480435719</v>
+      </c>
+      <c r="T22">
+        <v>0.899527605379524</v>
+      </c>
+      <c r="U22">
+        <v>0.0447</v>
+      </c>
+      <c r="V22">
+        <v>0.19</v>
+      </c>
+      <c r="W22">
+        <v>0.036207</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>13.56203973077551</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.08388492694940819</v>
+      </c>
+      <c r="C23">
+        <v>75.41341810457345</v>
+      </c>
+      <c r="D23">
+        <v>94.98541810457345</v>
+      </c>
+      <c r="E23">
+        <v>19.572</v>
+      </c>
+      <c r="F23">
+        <v>19.572</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>93.2</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>24.1</v>
+      </c>
+      <c r="K23">
+        <v>12.8</v>
+      </c>
+      <c r="L23">
+        <v>11.3</v>
+      </c>
+      <c r="M23">
+        <v>0.8748684</v>
+      </c>
+      <c r="N23">
+        <v>10.4251316</v>
+      </c>
+      <c r="O23">
+        <v>1.980775004</v>
+      </c>
+      <c r="P23">
+        <v>8.444356596</v>
+      </c>
+      <c r="Q23">
+        <v>21.244356596</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.09655880626507365</v>
+      </c>
+      <c r="T23">
+        <v>0.9091149282085118</v>
+      </c>
+      <c r="U23">
+        <v>0.0447</v>
+      </c>
+      <c r="V23">
+        <v>0.19</v>
+      </c>
+      <c r="W23">
+        <v>0.036207</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>12.91622831502429</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.08396471805533061</v>
+      </c>
+      <c r="C24">
+        <v>74.42197107554546</v>
+      </c>
+      <c r="D24">
+        <v>94.92597107554546</v>
+      </c>
+      <c r="E24">
+        <v>20.504</v>
+      </c>
+      <c r="F24">
+        <v>20.504</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>93.2</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>24.1</v>
+      </c>
+      <c r="K24">
+        <v>12.8</v>
+      </c>
+      <c r="L24">
+        <v>11.3</v>
+      </c>
+      <c r="M24">
+        <v>0.9390832000000001</v>
+      </c>
+      <c r="N24">
+        <v>10.3609168</v>
+      </c>
+      <c r="O24">
+        <v>1.968574192</v>
+      </c>
+      <c r="P24">
+        <v>8.392342608</v>
+      </c>
+      <c r="Q24">
+        <v>21.192342608</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.09718353596837258</v>
+      </c>
+      <c r="T24">
+        <v>0.9189480798279864</v>
+      </c>
+      <c r="U24">
+        <v>0.0458</v>
+      </c>
+      <c r="V24">
+        <v>0.19</v>
+      </c>
+      <c r="W24">
+        <v>0.03709800000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>12.03301262337565</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.08385739916125304</v>
+      </c>
+      <c r="C25">
+        <v>73.56994450132294</v>
+      </c>
+      <c r="D25">
+        <v>95.00594450132294</v>
+      </c>
+      <c r="E25">
+        <v>21.436</v>
+      </c>
+      <c r="F25">
+        <v>21.436</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>93.2</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>24.1</v>
+      </c>
+      <c r="K25">
+        <v>12.8</v>
+      </c>
+      <c r="L25">
+        <v>11.3</v>
+      </c>
+      <c r="M25">
+        <v>0.9817688</v>
+      </c>
+      <c r="N25">
+        <v>10.3182312</v>
+      </c>
+      <c r="O25">
+        <v>1.960463928</v>
+      </c>
+      <c r="P25">
+        <v>8.357767272</v>
+      </c>
+      <c r="Q25">
+        <v>21.157767272</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.09782449241721174</v>
+      </c>
+      <c r="T25">
+        <v>0.9290366379830318</v>
+      </c>
+      <c r="U25">
+        <v>0.0458</v>
+      </c>
+      <c r="V25">
+        <v>0.19</v>
+      </c>
+      <c r="W25">
+        <v>0.03709800000000001</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>11.50983816148975</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.08375008026717547</v>
+      </c>
+      <c r="C26">
+        <v>72.71805279307242</v>
+      </c>
+      <c r="D26">
+        <v>95.08605279307241</v>
+      </c>
+      <c r="E26">
+        <v>22.368</v>
+      </c>
+      <c r="F26">
+        <v>22.368</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>93.2</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>24.1</v>
+      </c>
+      <c r="K26">
+        <v>12.8</v>
+      </c>
+      <c r="L26">
+        <v>11.3</v>
+      </c>
+      <c r="M26">
+        <v>1.0244544</v>
+      </c>
+      <c r="N26">
+        <v>10.2755456</v>
+      </c>
+      <c r="O26">
+        <v>1.952353664</v>
+      </c>
+      <c r="P26">
+        <v>8.323191936000001</v>
+      </c>
+      <c r="Q26">
+        <v>21.123191936</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.09848231614102035</v>
+      </c>
+      <c r="T26">
+        <v>0.9393906845105785</v>
+      </c>
+      <c r="U26">
+        <v>0.0458</v>
+      </c>
+      <c r="V26">
+        <v>0.19</v>
+      </c>
+      <c r="W26">
+        <v>0.03709800000000001</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>11.03026157142768</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.08364276137309791</v>
+      </c>
+      <c r="C27">
+        <v>71.86629629223563</v>
+      </c>
+      <c r="D27">
+        <v>95.16629629223563</v>
+      </c>
+      <c r="E27">
+        <v>23.3</v>
+      </c>
+      <c r="F27">
+        <v>23.3</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>93.2</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>24.1</v>
+      </c>
+      <c r="K27">
+        <v>12.8</v>
+      </c>
+      <c r="L27">
+        <v>11.3</v>
+      </c>
+      <c r="M27">
+        <v>1.06714</v>
+      </c>
+      <c r="N27">
+        <v>10.23286</v>
+      </c>
+      <c r="O27">
+        <v>1.9442434</v>
+      </c>
+      <c r="P27">
+        <v>8.288616600000001</v>
+      </c>
+      <c r="Q27">
+        <v>21.0886166</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.09915768183079721</v>
+      </c>
+      <c r="T27">
+        <v>0.9500208389455264</v>
+      </c>
+      <c r="U27">
+        <v>0.0458</v>
+      </c>
+      <c r="V27">
+        <v>0.19</v>
+      </c>
+      <c r="W27">
+        <v>0.03709800000000001</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>10.58905110857057</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.08353544247902034</v>
+      </c>
+      <c r="C28">
+        <v>71.01467534140799</v>
+      </c>
+      <c r="D28">
+        <v>95.24667534140799</v>
+      </c>
+      <c r="E28">
+        <v>24.232</v>
+      </c>
+      <c r="F28">
+        <v>24.232</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>93.2</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>24.1</v>
+      </c>
+      <c r="K28">
+        <v>12.8</v>
+      </c>
+      <c r="L28">
+        <v>11.3</v>
+      </c>
+      <c r="M28">
+        <v>1.1098256</v>
+      </c>
+      <c r="N28">
+        <v>10.1901744</v>
+      </c>
+      <c r="O28">
+        <v>1.936133136</v>
+      </c>
+      <c r="P28">
+        <v>8.254041264</v>
+      </c>
+      <c r="Q28">
+        <v>21.054041264</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.09985130064732478</v>
+      </c>
+      <c r="T28">
+        <v>0.9609382948516891</v>
+      </c>
+      <c r="U28">
+        <v>0.0458</v>
+      </c>
+      <c r="V28">
+        <v>0.19</v>
+      </c>
+      <c r="W28">
+        <v>0.03709800000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>10.18177991208709</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.08390926358494277</v>
+      </c>
+      <c r="C29">
+        <v>69.80327861121572</v>
+      </c>
+      <c r="D29">
+        <v>94.96727861121572</v>
+      </c>
+      <c r="E29">
+        <v>25.164</v>
+      </c>
+      <c r="F29">
+        <v>25.164</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>93.2</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>24.1</v>
+      </c>
+      <c r="K29">
+        <v>12.8</v>
+      </c>
+      <c r="L29">
+        <v>11.3</v>
+      </c>
+      <c r="M29">
+        <v>1.207872</v>
+      </c>
+      <c r="N29">
+        <v>10.092128</v>
+      </c>
+      <c r="O29">
+        <v>1.91750432</v>
+      </c>
+      <c r="P29">
+        <v>8.17462368</v>
+      </c>
+      <c r="Q29">
+        <v>20.97462368</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1005639227190997</v>
+      </c>
+      <c r="T29">
+        <v>0.9721548591388425</v>
+      </c>
+      <c r="U29">
+        <v>0.048</v>
+      </c>
+      <c r="V29">
+        <v>0.19</v>
+      </c>
+      <c r="W29">
+        <v>0.03888</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>9.355295925396069</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.08381976469086519</v>
+      </c>
+      <c r="C30">
+        <v>68.93802141577221</v>
+      </c>
+      <c r="D30">
+        <v>95.03402141577222</v>
+      </c>
+      <c r="E30">
+        <v>26.096</v>
+      </c>
+      <c r="F30">
+        <v>26.096</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>93.2</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>24.1</v>
+      </c>
+      <c r="K30">
+        <v>12.8</v>
+      </c>
+      <c r="L30">
+        <v>11.3</v>
+      </c>
+      <c r="M30">
+        <v>1.252608</v>
+      </c>
+      <c r="N30">
+        <v>10.047392</v>
+      </c>
+      <c r="O30">
+        <v>1.90900448</v>
+      </c>
+      <c r="P30">
+        <v>8.13838752</v>
+      </c>
+      <c r="Q30">
+        <v>20.93838752</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1012963398484239</v>
+      </c>
+      <c r="T30">
+        <v>0.9836829946561946</v>
+      </c>
+      <c r="U30">
+        <v>0.048</v>
+      </c>
+      <c r="V30">
+        <v>0.19</v>
+      </c>
+      <c r="W30">
+        <v>0.03888</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>9.02117821377478</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.08373026579678761</v>
+      </c>
+      <c r="C31">
+        <v>68.0728580997135</v>
+      </c>
+      <c r="D31">
+        <v>95.10085809971351</v>
+      </c>
+      <c r="E31">
+        <v>27.028</v>
+      </c>
+      <c r="F31">
+        <v>27.028</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>93.2</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>24.1</v>
+      </c>
+      <c r="K31">
+        <v>12.8</v>
+      </c>
+      <c r="L31">
+        <v>11.3</v>
+      </c>
+      <c r="M31">
+        <v>1.297344</v>
+      </c>
+      <c r="N31">
+        <v>10.002656</v>
+      </c>
+      <c r="O31">
+        <v>1.90050464</v>
+      </c>
+      <c r="P31">
+        <v>8.102151360000001</v>
+      </c>
+      <c r="Q31">
+        <v>20.90215136</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1020493884461797</v>
+      </c>
+      <c r="T31">
+        <v>0.9955358663853031</v>
+      </c>
+      <c r="U31">
+        <v>0.048</v>
+      </c>
+      <c r="V31">
+        <v>0.19</v>
+      </c>
+      <c r="W31">
+        <v>0.03888</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>8.71010310295496</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.08364076690271005</v>
+      </c>
+      <c r="C32">
+        <v>67.20778886125291</v>
+      </c>
+      <c r="D32">
+        <v>95.16778886125292</v>
+      </c>
+      <c r="E32">
+        <v>27.96</v>
+      </c>
+      <c r="F32">
+        <v>27.96</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>93.2</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>24.1</v>
+      </c>
+      <c r="K32">
+        <v>12.8</v>
+      </c>
+      <c r="L32">
+        <v>11.3</v>
+      </c>
+      <c r="M32">
+        <v>1.34208</v>
+      </c>
+      <c r="N32">
+        <v>9.957920000000001</v>
+      </c>
+      <c r="O32">
+        <v>1.8920048</v>
+      </c>
+      <c r="P32">
+        <v>8.065915200000001</v>
+      </c>
+      <c r="Q32">
+        <v>20.8659152</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1028239527181572</v>
+      </c>
+      <c r="T32">
+        <v>1.007727391592386</v>
+      </c>
+      <c r="U32">
+        <v>0.048</v>
+      </c>
+      <c r="V32">
+        <v>0.19</v>
+      </c>
+      <c r="W32">
+        <v>0.03888</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>8.419766332856462</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.08355126800863248</v>
+      </c>
+      <c r="C33">
+        <v>66.34281389916217</v>
+      </c>
+      <c r="D33">
+        <v>95.23481389916216</v>
+      </c>
+      <c r="E33">
+        <v>28.892</v>
+      </c>
+      <c r="F33">
+        <v>28.892</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>93.2</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>24.1</v>
+      </c>
+      <c r="K33">
+        <v>12.8</v>
+      </c>
+      <c r="L33">
+        <v>11.3</v>
+      </c>
+      <c r="M33">
+        <v>1.386816</v>
+      </c>
+      <c r="N33">
+        <v>9.913184000000001</v>
+      </c>
+      <c r="O33">
+        <v>1.88350496</v>
+      </c>
+      <c r="P33">
+        <v>8.029679040000001</v>
+      </c>
+      <c r="Q33">
+        <v>20.82967904</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1036209681284529</v>
+      </c>
+      <c r="T33">
+        <v>1.020272294341704</v>
+      </c>
+      <c r="U33">
+        <v>0.048</v>
+      </c>
+      <c r="V33">
+        <v>0.19</v>
+      </c>
+      <c r="W33">
+        <v>0.03888</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>8.148160967280447</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.0834617691145549</v>
+      </c>
+      <c r="C34">
+        <v>65.47793341277334</v>
+      </c>
+      <c r="D34">
+        <v>95.30193341277334</v>
+      </c>
+      <c r="E34">
+        <v>29.824</v>
+      </c>
+      <c r="F34">
+        <v>29.824</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>93.2</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>24.1</v>
+      </c>
+      <c r="K34">
+        <v>12.8</v>
+      </c>
+      <c r="L34">
+        <v>11.3</v>
+      </c>
+      <c r="M34">
+        <v>1.431552</v>
+      </c>
+      <c r="N34">
+        <v>9.868448000000001</v>
+      </c>
+      <c r="O34">
+        <v>1.87500512</v>
+      </c>
+      <c r="P34">
+        <v>7.993442880000001</v>
+      </c>
+      <c r="Q34">
+        <v>20.79344288</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1044414251684631</v>
+      </c>
+      <c r="T34">
+        <v>1.033186164818942</v>
+      </c>
+      <c r="U34">
+        <v>0.048</v>
+      </c>
+      <c r="V34">
+        <v>0.19</v>
+      </c>
+      <c r="W34">
+        <v>0.03888</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>7.893530937052932</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.08377322022047733</v>
+      </c>
+      <c r="C35">
+        <v>64.31276853075342</v>
+      </c>
+      <c r="D35">
+        <v>95.06876853075342</v>
+      </c>
+      <c r="E35">
+        <v>30.756</v>
+      </c>
+      <c r="F35">
+        <v>30.756</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>93.2</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>24.1</v>
+      </c>
+      <c r="K35">
+        <v>12.8</v>
+      </c>
+      <c r="L35">
+        <v>11.3</v>
+      </c>
+      <c r="M35">
+        <v>1.522422</v>
+      </c>
+      <c r="N35">
+        <v>9.777578</v>
+      </c>
+      <c r="O35">
+        <v>1.85773982</v>
+      </c>
+      <c r="P35">
+        <v>7.91983818</v>
+      </c>
+      <c r="Q35">
+        <v>20.71983818</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.105286373463399</v>
+      </c>
+      <c r="T35">
+        <v>1.046485523967143</v>
+      </c>
+      <c r="U35">
+        <v>0.0495</v>
+      </c>
+      <c r="V35">
+        <v>0.19</v>
+      </c>
+      <c r="W35">
+        <v>0.04009500000000001</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>7.422383544115888</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.08369587132639976</v>
+      </c>
+      <c r="C36">
+        <v>63.43856848446076</v>
+      </c>
+      <c r="D36">
+        <v>95.12656848446076</v>
+      </c>
+      <c r="E36">
+        <v>31.688</v>
+      </c>
+      <c r="F36">
+        <v>31.688</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>93.2</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>24.1</v>
+      </c>
+      <c r="K36">
+        <v>12.8</v>
+      </c>
+      <c r="L36">
+        <v>11.3</v>
+      </c>
+      <c r="M36">
+        <v>1.568556</v>
+      </c>
+      <c r="N36">
+        <v>9.731444</v>
+      </c>
+      <c r="O36">
+        <v>1.84897436</v>
+      </c>
+      <c r="P36">
+        <v>7.88246964</v>
+      </c>
+      <c r="Q36">
+        <v>20.68246964</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1061569262521209</v>
+      </c>
+      <c r="T36">
+        <v>1.060187893998623</v>
+      </c>
+      <c r="U36">
+        <v>0.0495</v>
+      </c>
+      <c r="V36">
+        <v>0.19</v>
+      </c>
+      <c r="W36">
+        <v>0.04009500000000001</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>7.204078145759538</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.08361852243232218</v>
+      </c>
+      <c r="C37">
+        <v>62.56443876340947</v>
+      </c>
+      <c r="D37">
+        <v>95.18443876340947</v>
+      </c>
+      <c r="E37">
+        <v>32.62</v>
+      </c>
+      <c r="F37">
+        <v>32.62</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>93.2</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>24.1</v>
+      </c>
+      <c r="K37">
+        <v>12.8</v>
+      </c>
+      <c r="L37">
+        <v>11.3</v>
+      </c>
+      <c r="M37">
+        <v>1.61469</v>
+      </c>
+      <c r="N37">
+        <v>9.685310000000001</v>
+      </c>
+      <c r="O37">
+        <v>1.8402089</v>
+      </c>
+      <c r="P37">
+        <v>7.845101100000001</v>
+      </c>
+      <c r="Q37">
+        <v>20.6451011</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1070542652804957</v>
+      </c>
+      <c r="T37">
+        <v>1.074311875415686</v>
+      </c>
+      <c r="U37">
+        <v>0.0495</v>
+      </c>
+      <c r="V37">
+        <v>0.19</v>
+      </c>
+      <c r="W37">
+        <v>0.04009500000000001</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>6.99824734159498</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.08354117353824461</v>
+      </c>
+      <c r="C38">
+        <v>61.69037949602481</v>
+      </c>
+      <c r="D38">
+        <v>95.24237949602481</v>
+      </c>
+      <c r="E38">
+        <v>33.552</v>
+      </c>
+      <c r="F38">
+        <v>33.552</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>93.2</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>24.1</v>
+      </c>
+      <c r="K38">
+        <v>12.8</v>
+      </c>
+      <c r="L38">
+        <v>11.3</v>
+      </c>
+      <c r="M38">
+        <v>1.660824</v>
+      </c>
+      <c r="N38">
+        <v>9.639176000000001</v>
+      </c>
+      <c r="O38">
+        <v>1.83144344</v>
+      </c>
+      <c r="P38">
+        <v>7.807732560000001</v>
+      </c>
+      <c r="Q38">
+        <v>20.60773256</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1079796461535072</v>
+      </c>
+      <c r="T38">
+        <v>1.088877231252033</v>
+      </c>
+      <c r="U38">
+        <v>0.0495</v>
+      </c>
+      <c r="V38">
+        <v>0.19</v>
+      </c>
+      <c r="W38">
+        <v>0.04009500000000001</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>6.803851582106232</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.08346382464416706</v>
+      </c>
+      <c r="C39">
+        <v>60.81639081104496</v>
+      </c>
+      <c r="D39">
+        <v>95.30039081104496</v>
+      </c>
+      <c r="E39">
+        <v>34.484</v>
+      </c>
+      <c r="F39">
+        <v>34.484</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>93.2</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>24.1</v>
+      </c>
+      <c r="K39">
+        <v>12.8</v>
+      </c>
+      <c r="L39">
+        <v>11.3</v>
+      </c>
+      <c r="M39">
+        <v>1.706958</v>
+      </c>
+      <c r="N39">
+        <v>9.593042000000001</v>
+      </c>
+      <c r="O39">
+        <v>1.82267798</v>
+      </c>
+      <c r="P39">
+        <v>7.770364020000001</v>
+      </c>
+      <c r="Q39">
+        <v>20.57036402</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1089344041970906</v>
+      </c>
+      <c r="T39">
+        <v>1.103904979337153</v>
+      </c>
+      <c r="U39">
+        <v>0.0495</v>
+      </c>
+      <c r="V39">
+        <v>0.19</v>
+      </c>
+      <c r="W39">
+        <v>0.04009500000000001</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>6.619963701508765</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.08338647575008948</v>
+      </c>
+      <c r="C40">
+        <v>59.94247283752195</v>
+      </c>
+      <c r="D40">
+        <v>95.35847283752196</v>
+      </c>
+      <c r="E40">
+        <v>35.416</v>
+      </c>
+      <c r="F40">
+        <v>35.416</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>93.2</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>24.1</v>
+      </c>
+      <c r="K40">
+        <v>12.8</v>
+      </c>
+      <c r="L40">
+        <v>11.3</v>
+      </c>
+      <c r="M40">
+        <v>1.753092</v>
+      </c>
+      <c r="N40">
+        <v>9.546908</v>
+      </c>
+      <c r="O40">
+        <v>1.81391252</v>
+      </c>
+      <c r="P40">
+        <v>7.73299548</v>
+      </c>
+      <c r="Q40">
+        <v>20.53299548</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1099199608872411</v>
+      </c>
+      <c r="T40">
+        <v>1.119417493489534</v>
+      </c>
+      <c r="U40">
+        <v>0.0495</v>
+      </c>
+      <c r="V40">
+        <v>0.19</v>
+      </c>
+      <c r="W40">
+        <v>0.04009500000000001</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>6.445754130416429</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.08330912685601191</v>
+      </c>
+      <c r="C41">
+        <v>59.06862570482257</v>
+      </c>
+      <c r="D41">
+        <v>95.41662570482256</v>
+      </c>
+      <c r="E41">
+        <v>36.348</v>
+      </c>
+      <c r="F41">
+        <v>36.348</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>93.2</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>24.1</v>
+      </c>
+      <c r="K41">
+        <v>12.8</v>
+      </c>
+      <c r="L41">
+        <v>11.3</v>
+      </c>
+      <c r="M41">
+        <v>1.799226</v>
+      </c>
+      <c r="N41">
+        <v>9.500774</v>
+      </c>
+      <c r="O41">
+        <v>1.80514706</v>
+      </c>
+      <c r="P41">
+        <v>7.69562694</v>
+      </c>
+      <c r="Q41">
+        <v>20.49562694</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1109378309114949</v>
+      </c>
+      <c r="T41">
+        <v>1.135438614663306</v>
+      </c>
+      <c r="U41">
+        <v>0.0495</v>
+      </c>
+      <c r="V41">
+        <v>0.19</v>
+      </c>
+      <c r="W41">
+        <v>0.04009500000000001</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>6.280478383482675</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.08368537796193434</v>
+      </c>
+      <c r="C42">
+        <v>57.85441520027496</v>
+      </c>
+      <c r="D42">
+        <v>95.13441520027496</v>
+      </c>
+      <c r="E42">
+        <v>37.28</v>
+      </c>
+      <c r="F42">
+        <v>37.28</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>93.2</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>24.1</v>
+      </c>
+      <c r="K42">
+        <v>12.8</v>
+      </c>
+      <c r="L42">
+        <v>11.3</v>
+      </c>
+      <c r="M42">
+        <v>1.897552</v>
+      </c>
+      <c r="N42">
+        <v>9.402448</v>
+      </c>
+      <c r="O42">
+        <v>1.78646512</v>
+      </c>
+      <c r="P42">
+        <v>7.61598288</v>
+      </c>
+      <c r="Q42">
+        <v>20.41598288</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1119896299365572</v>
+      </c>
+      <c r="T42">
+        <v>1.151993773209536</v>
+      </c>
+      <c r="U42">
+        <v>0.0509</v>
+      </c>
+      <c r="V42">
+        <v>0.19</v>
+      </c>
+      <c r="W42">
+        <v>0.041229</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>5.955041021273725</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.08361936906785677</v>
+      </c>
+      <c r="C43">
+        <v>56.9718049532582</v>
+      </c>
+      <c r="D43">
+        <v>95.1838049532582</v>
+      </c>
+      <c r="E43">
+        <v>38.212</v>
+      </c>
+      <c r="F43">
+        <v>38.212</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>93.2</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>24.1</v>
+      </c>
+      <c r="K43">
+        <v>12.8</v>
+      </c>
+      <c r="L43">
+        <v>11.3</v>
+      </c>
+      <c r="M43">
+        <v>1.9449908</v>
+      </c>
+      <c r="N43">
+        <v>9.355009200000001</v>
+      </c>
+      <c r="O43">
+        <v>1.777451748</v>
+      </c>
+      <c r="P43">
+        <v>7.577557452000001</v>
+      </c>
+      <c r="Q43">
+        <v>20.377557452</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1130770831658589</v>
+      </c>
+      <c r="T43">
+        <v>1.169110123570893</v>
+      </c>
+      <c r="U43">
+        <v>0.0509</v>
+      </c>
+      <c r="V43">
+        <v>0.19</v>
+      </c>
+      <c r="W43">
+        <v>0.041229</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>5.80979611831583</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.08355336017377921</v>
+      </c>
+      <c r="C44">
+        <v>56.08924601500831</v>
+      </c>
+      <c r="D44">
+        <v>95.23324601500831</v>
+      </c>
+      <c r="E44">
+        <v>39.144</v>
+      </c>
+      <c r="F44">
+        <v>39.144</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>93.2</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>24.1</v>
+      </c>
+      <c r="K44">
+        <v>12.8</v>
+      </c>
+      <c r="L44">
+        <v>11.3</v>
+      </c>
+      <c r="M44">
+        <v>1.9924296</v>
+      </c>
+      <c r="N44">
+        <v>9.307570400000001</v>
+      </c>
+      <c r="O44">
+        <v>1.768438376</v>
+      </c>
+      <c r="P44">
+        <v>7.539132024000001</v>
+      </c>
+      <c r="Q44">
+        <v>20.339132024</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1142020347823779</v>
+      </c>
+      <c r="T44">
+        <v>1.186816692910227</v>
+      </c>
+      <c r="U44">
+        <v>0.0509</v>
+      </c>
+      <c r="V44">
+        <v>0.19</v>
+      </c>
+      <c r="W44">
+        <v>0.041229</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>5.671467639308311</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.08348735127970162</v>
+      </c>
+      <c r="C45">
+        <v>55.20673846552028</v>
+      </c>
+      <c r="D45">
+        <v>95.28273846552028</v>
+      </c>
+      <c r="E45">
+        <v>40.076</v>
+      </c>
+      <c r="F45">
+        <v>40.076</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>93.2</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>24.1</v>
+      </c>
+      <c r="K45">
+        <v>12.8</v>
+      </c>
+      <c r="L45">
+        <v>11.3</v>
+      </c>
+      <c r="M45">
+        <v>2.0398684</v>
+      </c>
+      <c r="N45">
+        <v>9.260131600000001</v>
+      </c>
+      <c r="O45">
+        <v>1.759425004</v>
+      </c>
+      <c r="P45">
+        <v>7.500706596000001</v>
+      </c>
+      <c r="Q45">
+        <v>20.300706596</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1153664583854414</v>
+      </c>
+      <c r="T45">
+        <v>1.205144545384275</v>
+      </c>
+      <c r="U45">
+        <v>0.0509</v>
+      </c>
+      <c r="V45">
+        <v>0.19</v>
+      </c>
+      <c r="W45">
+        <v>0.041229</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>5.539573043045326</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.08342134238562407</v>
+      </c>
+      <c r="C46">
+        <v>54.32428238495559</v>
+      </c>
+      <c r="D46">
+        <v>95.33228238495559</v>
+      </c>
+      <c r="E46">
+        <v>41.008</v>
+      </c>
+      <c r="F46">
+        <v>41.008</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>93.2</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>24.1</v>
+      </c>
+      <c r="K46">
+        <v>12.8</v>
+      </c>
+      <c r="L46">
+        <v>11.3</v>
+      </c>
+      <c r="M46">
+        <v>2.0873072</v>
+      </c>
+      <c r="N46">
+        <v>9.212692800000001</v>
+      </c>
+      <c r="O46">
+        <v>1.750411632</v>
+      </c>
+      <c r="P46">
+        <v>7.462281168000001</v>
+      </c>
+      <c r="Q46">
+        <v>20.262281168</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1165724685457573</v>
+      </c>
+      <c r="T46">
+        <v>1.224126964018111</v>
+      </c>
+      <c r="U46">
+        <v>0.0509</v>
+      </c>
+      <c r="V46">
+        <v>0.19</v>
+      </c>
+      <c r="W46">
+        <v>0.041229</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>5.413673655703387</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.08335533349154649</v>
+      </c>
+      <c r="C47">
+        <v>53.44187785364252</v>
+      </c>
+      <c r="D47">
+        <v>95.38187785364252</v>
+      </c>
+      <c r="E47">
+        <v>41.94</v>
+      </c>
+      <c r="F47">
+        <v>41.94</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>93.2</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>24.1</v>
+      </c>
+      <c r="K47">
+        <v>12.8</v>
+      </c>
+      <c r="L47">
+        <v>11.3</v>
+      </c>
+      <c r="M47">
+        <v>2.134746</v>
+      </c>
+      <c r="N47">
+        <v>9.165254000000001</v>
+      </c>
+      <c r="O47">
+        <v>1.74139826</v>
+      </c>
+      <c r="P47">
+        <v>7.42385574</v>
+      </c>
+      <c r="Q47">
+        <v>20.22385574</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1178223336209936</v>
+      </c>
+      <c r="T47">
+        <v>1.243799652420449</v>
+      </c>
+      <c r="U47">
+        <v>0.0509</v>
+      </c>
+      <c r="V47">
+        <v>0.19</v>
+      </c>
+      <c r="W47">
+        <v>0.041229</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>5.293369796687756</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.08328932459746892</v>
+      </c>
+      <c r="C48">
+        <v>52.55952495207653</v>
+      </c>
+      <c r="D48">
+        <v>95.43152495207653</v>
+      </c>
+      <c r="E48">
+        <v>42.872</v>
+      </c>
+      <c r="F48">
+        <v>42.872</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>93.2</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>24.1</v>
+      </c>
+      <c r="K48">
+        <v>12.8</v>
+      </c>
+      <c r="L48">
+        <v>11.3</v>
+      </c>
+      <c r="M48">
+        <v>2.1821848</v>
+      </c>
+      <c r="N48">
+        <v>9.117815200000001</v>
+      </c>
+      <c r="O48">
+        <v>1.732384888</v>
+      </c>
+      <c r="P48">
+        <v>7.385430312</v>
+      </c>
+      <c r="Q48">
+        <v>20.185430312</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1191184899953128</v>
+      </c>
+      <c r="T48">
+        <v>1.264200958911763</v>
+      </c>
+      <c r="U48">
+        <v>0.0509</v>
+      </c>
+      <c r="V48">
+        <v>0.19</v>
+      </c>
+      <c r="W48">
+        <v>0.041229</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>5.178296540238023</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.08322331570339135</v>
+      </c>
+      <c r="C49">
+        <v>51.67722376092084</v>
+      </c>
+      <c r="D49">
+        <v>95.48122376092084</v>
+      </c>
+      <c r="E49">
+        <v>43.804</v>
+      </c>
+      <c r="F49">
+        <v>43.804</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>93.2</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>24.1</v>
+      </c>
+      <c r="K49">
+        <v>12.8</v>
+      </c>
+      <c r="L49">
+        <v>11.3</v>
+      </c>
+      <c r="M49">
+        <v>2.2296236</v>
+      </c>
+      <c r="N49">
+        <v>9.070376400000001</v>
+      </c>
+      <c r="O49">
+        <v>1.723371516</v>
+      </c>
+      <c r="P49">
+        <v>7.347004884</v>
+      </c>
+      <c r="Q49">
+        <v>20.147004884</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1204635579309271</v>
+      </c>
+      <c r="T49">
+        <v>1.285372126025391</v>
+      </c>
+      <c r="U49">
+        <v>0.0509</v>
+      </c>
+      <c r="V49">
+        <v>0.19</v>
+      </c>
+      <c r="W49">
+        <v>0.041229</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>5.068120018105298</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.08315730680931378</v>
+      </c>
+      <c r="C50">
+        <v>50.79497436100673</v>
+      </c>
+      <c r="D50">
+        <v>95.53097436100673</v>
+      </c>
+      <c r="E50">
+        <v>44.736</v>
+      </c>
+      <c r="F50">
+        <v>44.736</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>93.2</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>24.1</v>
+      </c>
+      <c r="K50">
+        <v>12.8</v>
+      </c>
+      <c r="L50">
+        <v>11.3</v>
+      </c>
+      <c r="M50">
+        <v>2.2770624</v>
+      </c>
+      <c r="N50">
+        <v>9.022937600000001</v>
+      </c>
+      <c r="O50">
+        <v>1.714358144</v>
+      </c>
+      <c r="P50">
+        <v>7.308579456</v>
+      </c>
+      <c r="Q50">
+        <v>20.108579456</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1218603592486803</v>
+      </c>
+      <c r="T50">
+        <v>1.307357568797236</v>
+      </c>
+      <c r="U50">
+        <v>0.0509</v>
+      </c>
+      <c r="V50">
+        <v>0.19</v>
+      </c>
+      <c r="W50">
+        <v>0.041229</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>4.962534184394771</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.0830912979152362</v>
+      </c>
+      <c r="C51">
+        <v>49.91277683333409</v>
+      </c>
+      <c r="D51">
+        <v>95.58077683333408</v>
+      </c>
+      <c r="E51">
+        <v>45.668</v>
+      </c>
+      <c r="F51">
+        <v>45.668</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>93.2</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>24.1</v>
+      </c>
+      <c r="K51">
+        <v>12.8</v>
+      </c>
+      <c r="L51">
+        <v>11.3</v>
+      </c>
+      <c r="M51">
+        <v>2.3245012</v>
+      </c>
+      <c r="N51">
+        <v>8.9754988</v>
+      </c>
+      <c r="O51">
+        <v>1.705344772</v>
+      </c>
+      <c r="P51">
+        <v>7.270154028</v>
+      </c>
+      <c r="Q51">
+        <v>20.070154028</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1233119370886984</v>
+      </c>
+      <c r="T51">
+        <v>1.330205185795427</v>
+      </c>
+      <c r="U51">
+        <v>0.0509</v>
+      </c>
+      <c r="V51">
+        <v>0.19</v>
+      </c>
+      <c r="W51">
+        <v>0.041229</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>4.861257976549981</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.08302528902115863</v>
+      </c>
+      <c r="C52">
+        <v>49.03063125907172</v>
+      </c>
+      <c r="D52">
+        <v>95.63063125907172</v>
+      </c>
+      <c r="E52">
+        <v>46.6</v>
+      </c>
+      <c r="F52">
+        <v>46.6</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>93.2</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>24.1</v>
+      </c>
+      <c r="K52">
+        <v>12.8</v>
+      </c>
+      <c r="L52">
+        <v>11.3</v>
+      </c>
+      <c r="M52">
+        <v>2.37194</v>
+      </c>
+      <c r="N52">
+        <v>8.92806</v>
+      </c>
+      <c r="O52">
+        <v>1.6963314</v>
+      </c>
+      <c r="P52">
+        <v>7.2317286</v>
+      </c>
+      <c r="Q52">
+        <v>20.0317286</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1248215780423173</v>
+      </c>
+      <c r="T52">
+        <v>1.353966707473546</v>
+      </c>
+      <c r="U52">
+        <v>0.0509</v>
+      </c>
+      <c r="V52">
+        <v>0.19</v>
+      </c>
+      <c r="W52">
+        <v>0.041229</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>4.764032817018981</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.08295928012708105</v>
+      </c>
+      <c r="C53">
+        <v>48.148537719558</v>
+      </c>
+      <c r="D53">
+        <v>95.680537719558</v>
+      </c>
+      <c r="E53">
+        <v>47.532</v>
+      </c>
+      <c r="F53">
+        <v>47.532</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>93.2</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>24.1</v>
+      </c>
+      <c r="K53">
+        <v>12.8</v>
+      </c>
+      <c r="L53">
+        <v>11.3</v>
+      </c>
+      <c r="M53">
+        <v>2.4193788</v>
+      </c>
+      <c r="N53">
+        <v>8.8806212</v>
+      </c>
+      <c r="O53">
+        <v>1.687318028</v>
+      </c>
+      <c r="P53">
+        <v>7.193303172</v>
+      </c>
+      <c r="Q53">
+        <v>19.993303172</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.126392836994043</v>
+      </c>
+      <c r="T53">
+        <v>1.378698087179343</v>
+      </c>
+      <c r="U53">
+        <v>0.0509</v>
+      </c>
+      <c r="V53">
+        <v>0.19</v>
+      </c>
+      <c r="W53">
+        <v>0.041229</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>4.670620408842137</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.0828932712330035</v>
+      </c>
+      <c r="C54">
+        <v>47.26649629630101</v>
+      </c>
+      <c r="D54">
+        <v>95.73049629630101</v>
+      </c>
+      <c r="E54">
+        <v>48.46400000000001</v>
+      </c>
+      <c r="F54">
+        <v>48.46400000000001</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>93.2</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>24.1</v>
+      </c>
+      <c r="K54">
+        <v>12.8</v>
+      </c>
+      <c r="L54">
+        <v>11.3</v>
+      </c>
+      <c r="M54">
+        <v>2.4668176</v>
+      </c>
+      <c r="N54">
+        <v>8.8331824</v>
+      </c>
+      <c r="O54">
+        <v>1.678304656</v>
+      </c>
+      <c r="P54">
+        <v>7.154877744</v>
+      </c>
+      <c r="Q54">
+        <v>19.954877744</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1280295650687573</v>
+      </c>
+      <c r="T54">
+        <v>1.404459941039548</v>
+      </c>
+      <c r="U54">
+        <v>0.0509</v>
+      </c>
+      <c r="V54">
+        <v>0.19</v>
+      </c>
+      <c r="W54">
+        <v>0.041229</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>4.580800785595173</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.08394344233892592</v>
+      </c>
+      <c r="C55">
+        <v>45.54581491575695</v>
+      </c>
+      <c r="D55">
+        <v>94.94181491575695</v>
+      </c>
+      <c r="E55">
+        <v>49.396</v>
+      </c>
+      <c r="F55">
+        <v>49.396</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>93.2</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>24.1</v>
+      </c>
+      <c r="K55">
+        <v>12.8</v>
+      </c>
+      <c r="L55">
+        <v>11.3</v>
+      </c>
+      <c r="M55">
+        <v>2.642686</v>
+      </c>
+      <c r="N55">
+        <v>8.657314000000001</v>
+      </c>
+      <c r="O55">
+        <v>1.64488966</v>
+      </c>
+      <c r="P55">
+        <v>7.012424340000001</v>
+      </c>
+      <c r="Q55">
+        <v>19.81242434</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1297359411466509</v>
+      </c>
+      <c r="T55">
+        <v>1.431318044000188</v>
+      </c>
+      <c r="U55">
+        <v>0.0535</v>
+      </c>
+      <c r="V55">
+        <v>0.19</v>
+      </c>
+      <c r="W55">
+        <v>0.04333500000000001</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>4.275952572496317</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.08389849344484836</v>
+      </c>
+      <c r="C56">
+        <v>44.64730536103723</v>
+      </c>
+      <c r="D56">
+        <v>94.97530536103723</v>
+      </c>
+      <c r="E56">
+        <v>50.328</v>
+      </c>
+      <c r="F56">
+        <v>50.328</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>93.2</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>24.1</v>
+      </c>
+      <c r="K56">
+        <v>12.8</v>
+      </c>
+      <c r="L56">
+        <v>11.3</v>
+      </c>
+      <c r="M56">
+        <v>2.692548</v>
+      </c>
+      <c r="N56">
+        <v>8.607452</v>
+      </c>
+      <c r="O56">
+        <v>1.63541588</v>
+      </c>
+      <c r="P56">
+        <v>6.97203612</v>
+      </c>
+      <c r="Q56">
+        <v>19.77203612</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1315165074888008</v>
+      </c>
+      <c r="T56">
+        <v>1.459343890567812</v>
+      </c>
+      <c r="U56">
+        <v>0.0535</v>
+      </c>
+      <c r="V56">
+        <v>0.19</v>
+      </c>
+      <c r="W56">
+        <v>0.04333500000000001</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>4.196768265598236</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.08385354455077078</v>
+      </c>
+      <c r="C57">
+        <v>43.74881944196657</v>
+      </c>
+      <c r="D57">
+        <v>95.00881944196658</v>
+      </c>
+      <c r="E57">
+        <v>51.26000000000001</v>
+      </c>
+      <c r="F57">
+        <v>51.26000000000001</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>93.2</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>24.1</v>
+      </c>
+      <c r="K57">
+        <v>12.8</v>
+      </c>
+      <c r="L57">
+        <v>11.3</v>
+      </c>
+      <c r="M57">
+        <v>2.74241</v>
+      </c>
+      <c r="N57">
+        <v>8.557590000000001</v>
+      </c>
+      <c r="O57">
+        <v>1.6259421</v>
+      </c>
+      <c r="P57">
+        <v>6.931647900000001</v>
+      </c>
+      <c r="Q57">
+        <v>19.7316479</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.133376210112824</v>
+      </c>
+      <c r="T57">
+        <v>1.488615330316219</v>
+      </c>
+      <c r="U57">
+        <v>0.0535</v>
+      </c>
+      <c r="V57">
+        <v>0.19</v>
+      </c>
+      <c r="W57">
+        <v>0.04333500000000001</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>4.120463388041905</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.08380859565669321</v>
+      </c>
+      <c r="C58">
+        <v>42.85035718357483</v>
+      </c>
+      <c r="D58">
+        <v>95.04235718357484</v>
+      </c>
+      <c r="E58">
+        <v>52.19200000000001</v>
+      </c>
+      <c r="F58">
+        <v>52.19200000000001</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>93.2</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>24.1</v>
+      </c>
+      <c r="K58">
+        <v>12.8</v>
+      </c>
+      <c r="L58">
+        <v>11.3</v>
+      </c>
+      <c r="M58">
+        <v>2.792272000000001</v>
+      </c>
+      <c r="N58">
+        <v>8.507728</v>
+      </c>
+      <c r="O58">
+        <v>1.61646832</v>
+      </c>
+      <c r="P58">
+        <v>6.89125968</v>
+      </c>
+      <c r="Q58">
+        <v>19.69125968</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1353204446743028</v>
+      </c>
+      <c r="T58">
+        <v>1.51921729005319</v>
+      </c>
+      <c r="U58">
+        <v>0.0535</v>
+      </c>
+      <c r="V58">
+        <v>0.19</v>
+      </c>
+      <c r="W58">
+        <v>0.04333500000000001</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>4.046883684684014</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.08501023676261564</v>
+      </c>
+      <c r="C59">
+        <v>41.02984432912106</v>
+      </c>
+      <c r="D59">
+        <v>94.15384432912107</v>
+      </c>
+      <c r="E59">
+        <v>53.12400000000001</v>
+      </c>
+      <c r="F59">
+        <v>53.12400000000001</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>93.2</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>24.1</v>
+      </c>
+      <c r="K59">
+        <v>12.8</v>
+      </c>
+      <c r="L59">
+        <v>11.3</v>
+      </c>
+      <c r="M59">
+        <v>2.985568800000001</v>
+      </c>
+      <c r="N59">
+        <v>8.3144312</v>
+      </c>
+      <c r="O59">
+        <v>1.579741928</v>
+      </c>
+      <c r="P59">
+        <v>6.734689272</v>
+      </c>
+      <c r="Q59">
+        <v>19.534689272</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1373551087502689</v>
+      </c>
+      <c r="T59">
+        <v>1.551242596754671</v>
+      </c>
+      <c r="U59">
+        <v>0.0562</v>
+      </c>
+      <c r="V59">
+        <v>0.19</v>
+      </c>
+      <c r="W59">
+        <v>0.045522</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>3.784873421774771</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.08498715786853807</v>
+      </c>
+      <c r="C60">
+        <v>40.11475273934423</v>
+      </c>
+      <c r="D60">
+        <v>94.17075273934422</v>
+      </c>
+      <c r="E60">
+        <v>54.056</v>
+      </c>
+      <c r="F60">
+        <v>54.056</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>93.2</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>24.1</v>
+      </c>
+      <c r="K60">
+        <v>12.8</v>
+      </c>
+      <c r="L60">
+        <v>11.3</v>
+      </c>
+      <c r="M60">
+        <v>3.0379472</v>
+      </c>
+      <c r="N60">
+        <v>8.262052800000001</v>
+      </c>
+      <c r="O60">
+        <v>1.569790032</v>
+      </c>
+      <c r="P60">
+        <v>6.692262768000001</v>
+      </c>
+      <c r="Q60">
+        <v>19.492262768</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1394866615917573</v>
+      </c>
+      <c r="T60">
+        <v>1.584792918060985</v>
+      </c>
+      <c r="U60">
+        <v>0.0562</v>
+      </c>
+      <c r="V60">
+        <v>0.19</v>
+      </c>
+      <c r="W60">
+        <v>0.045522</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>3.719616983468311</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.0849640789744605</v>
+      </c>
+      <c r="C61">
+        <v>39.19966722357719</v>
+      </c>
+      <c r="D61">
+        <v>94.18766722357719</v>
+      </c>
+      <c r="E61">
+        <v>54.988</v>
+      </c>
+      <c r="F61">
+        <v>54.988</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>93.2</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>24.1</v>
+      </c>
+      <c r="K61">
+        <v>12.8</v>
+      </c>
+      <c r="L61">
+        <v>11.3</v>
+      </c>
+      <c r="M61">
+        <v>3.0903256</v>
+      </c>
+      <c r="N61">
+        <v>8.209674400000001</v>
+      </c>
+      <c r="O61">
+        <v>1.559838136</v>
+      </c>
+      <c r="P61">
+        <v>6.649836264000001</v>
+      </c>
+      <c r="Q61">
+        <v>19.449836264</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1417221926206353</v>
+      </c>
+      <c r="T61">
+        <v>1.619979840406631</v>
+      </c>
+      <c r="U61">
+        <v>0.0562</v>
+      </c>
+      <c r="V61">
+        <v>0.19</v>
+      </c>
+      <c r="W61">
+        <v>0.045522</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>3.656572627816305</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.08494100008038293</v>
+      </c>
+      <c r="C62">
+        <v>38.28458778509352</v>
+      </c>
+      <c r="D62">
+        <v>94.20458778509352</v>
+      </c>
+      <c r="E62">
+        <v>55.92</v>
+      </c>
+      <c r="F62">
+        <v>55.92</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>93.2</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>24.1</v>
+      </c>
+      <c r="K62">
+        <v>12.8</v>
+      </c>
+      <c r="L62">
+        <v>11.3</v>
+      </c>
+      <c r="M62">
+        <v>3.142704</v>
+      </c>
+      <c r="N62">
+        <v>8.157296000000001</v>
+      </c>
+      <c r="O62">
+        <v>1.54988624</v>
+      </c>
+      <c r="P62">
+        <v>6.60740976</v>
+      </c>
+      <c r="Q62">
+        <v>19.40740976</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1440695002009573</v>
+      </c>
+      <c r="T62">
+        <v>1.65692610886956</v>
+      </c>
+      <c r="U62">
+        <v>0.0562</v>
+      </c>
+      <c r="V62">
+        <v>0.19</v>
+      </c>
+      <c r="W62">
+        <v>0.045522</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>3.595629750686034</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.08491792118630535</v>
+      </c>
+      <c r="C63">
+        <v>37.36951442716907</v>
+      </c>
+      <c r="D63">
+        <v>94.22151442716907</v>
+      </c>
+      <c r="E63">
+        <v>56.852</v>
+      </c>
+      <c r="F63">
+        <v>56.852</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>93.2</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>24.1</v>
+      </c>
+      <c r="K63">
+        <v>12.8</v>
+      </c>
+      <c r="L63">
+        <v>11.3</v>
+      </c>
+      <c r="M63">
+        <v>3.1950824</v>
+      </c>
+      <c r="N63">
+        <v>8.1049176</v>
+      </c>
+      <c r="O63">
+        <v>1.539934344</v>
+      </c>
+      <c r="P63">
+        <v>6.564983256</v>
+      </c>
+      <c r="Q63">
+        <v>19.364983256</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1465371825289881</v>
+      </c>
+      <c r="T63">
+        <v>1.695767057766485</v>
+      </c>
+      <c r="U63">
+        <v>0.0562</v>
+      </c>
+      <c r="V63">
+        <v>0.19</v>
+      </c>
+      <c r="W63">
+        <v>0.045522</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>3.536685000674787</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.08725518229222778</v>
+      </c>
+      <c r="C64">
+        <v>34.75364109094628</v>
+      </c>
+      <c r="D64">
+        <v>92.53764109094628</v>
+      </c>
+      <c r="E64">
+        <v>57.784</v>
+      </c>
+      <c r="F64">
+        <v>57.784</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>93.2</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>24.1</v>
+      </c>
+      <c r="K64">
+        <v>12.8</v>
+      </c>
+      <c r="L64">
+        <v>11.3</v>
+      </c>
+      <c r="M64">
+        <v>3.5190456</v>
+      </c>
+      <c r="N64">
+        <v>7.780954400000001</v>
+      </c>
+      <c r="O64">
+        <v>1.478381336</v>
+      </c>
+      <c r="P64">
+        <v>6.302573064000001</v>
+      </c>
+      <c r="Q64">
+        <v>19.102573064</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1491347428742836</v>
+      </c>
+      <c r="T64">
+        <v>1.736652267131669</v>
+      </c>
+      <c r="U64">
+        <v>0.0609</v>
+      </c>
+      <c r="V64">
+        <v>0.19</v>
+      </c>
+      <c r="W64">
+        <v>0.049329</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>3.211097918140078</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.08727017339815021</v>
+      </c>
+      <c r="C65">
+        <v>33.81103502248867</v>
+      </c>
+      <c r="D65">
+        <v>92.52703502248868</v>
+      </c>
+      <c r="E65">
+        <v>58.716</v>
+      </c>
+      <c r="F65">
+        <v>58.716</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>93.2</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>24.1</v>
+      </c>
+      <c r="K65">
+        <v>12.8</v>
+      </c>
+      <c r="L65">
+        <v>11.3</v>
+      </c>
+      <c r="M65">
+        <v>3.5758044</v>
+      </c>
+      <c r="N65">
+        <v>7.7241956</v>
+      </c>
+      <c r="O65">
+        <v>1.467597164</v>
+      </c>
+      <c r="P65">
+        <v>6.256598436</v>
+      </c>
+      <c r="Q65">
+        <v>19.056598436</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1518727118868924</v>
+      </c>
+      <c r="T65">
+        <v>1.77974748781389</v>
+      </c>
+      <c r="U65">
+        <v>0.0609</v>
+      </c>
+      <c r="V65">
+        <v>0.19</v>
+      </c>
+      <c r="W65">
+        <v>0.049329</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>3.160128109915632</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.08728516450407264</v>
+      </c>
+      <c r="C66">
+        <v>32.86843138495096</v>
+      </c>
+      <c r="D66">
+        <v>92.51643138495096</v>
+      </c>
+      <c r="E66">
+        <v>59.648</v>
+      </c>
+      <c r="F66">
+        <v>59.648</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>93.2</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>24.1</v>
+      </c>
+      <c r="K66">
+        <v>12.8</v>
+      </c>
+      <c r="L66">
+        <v>11.3</v>
+      </c>
+      <c r="M66">
+        <v>3.6325632</v>
+      </c>
+      <c r="N66">
+        <v>7.667436800000001</v>
+      </c>
+      <c r="O66">
+        <v>1.456812992</v>
+      </c>
+      <c r="P66">
+        <v>6.210623808000001</v>
+      </c>
+      <c r="Q66">
+        <v>19.010623808</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1547627902890907</v>
+      </c>
+      <c r="T66">
+        <v>1.825236887422901</v>
+      </c>
+      <c r="U66">
+        <v>0.0609</v>
+      </c>
+      <c r="V66">
+        <v>0.19</v>
+      </c>
+      <c r="W66">
+        <v>0.049329</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>3.1107511081982</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.08730015560999507</v>
+      </c>
+      <c r="C67">
+        <v>31.9258301774975</v>
+      </c>
+      <c r="D67">
+        <v>92.5058301774975</v>
+      </c>
+      <c r="E67">
+        <v>60.58000000000001</v>
+      </c>
+      <c r="F67">
+        <v>60.58000000000001</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>93.2</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>24.1</v>
+      </c>
+      <c r="K67">
+        <v>12.8</v>
+      </c>
+      <c r="L67">
+        <v>11.3</v>
+      </c>
+      <c r="M67">
+        <v>3.689322000000001</v>
+      </c>
+      <c r="N67">
+        <v>7.610678</v>
+      </c>
+      <c r="O67">
+        <v>1.44602882</v>
+      </c>
+      <c r="P67">
+        <v>6.16464918</v>
+      </c>
+      <c r="Q67">
+        <v>18.96464918</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1578180160285574</v>
+      </c>
+      <c r="T67">
+        <v>1.873325681295284</v>
+      </c>
+      <c r="U67">
+        <v>0.0609</v>
+      </c>
+      <c r="V67">
+        <v>0.19</v>
+      </c>
+      <c r="W67">
+        <v>0.049329</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>3.062893398841304</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.0873151467159175</v>
+      </c>
+      <c r="C68">
+        <v>30.98323139929301</v>
+      </c>
+      <c r="D68">
+        <v>92.49523139929302</v>
+      </c>
+      <c r="E68">
+        <v>61.51200000000001</v>
+      </c>
+      <c r="F68">
+        <v>61.51200000000001</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>93.2</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>24.1</v>
+      </c>
+      <c r="K68">
+        <v>12.8</v>
+      </c>
+      <c r="L68">
+        <v>11.3</v>
+      </c>
+      <c r="M68">
+        <v>3.746080800000001</v>
+      </c>
+      <c r="N68">
+        <v>7.5539192</v>
+      </c>
+      <c r="O68">
+        <v>1.435244648</v>
+      </c>
+      <c r="P68">
+        <v>6.118674552</v>
+      </c>
+      <c r="Q68">
+        <v>18.918674552</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1610529609291692</v>
+      </c>
+      <c r="T68">
+        <v>1.924243227748396</v>
+      </c>
+      <c r="U68">
+        <v>0.0609</v>
+      </c>
+      <c r="V68">
+        <v>0.19</v>
+      </c>
+      <c r="W68">
+        <v>0.049329</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>3.016485923101285</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.09237724782183994</v>
+      </c>
+      <c r="C69">
+        <v>26.60600482315745</v>
+      </c>
+      <c r="D69">
+        <v>89.05000482315745</v>
+      </c>
+      <c r="E69">
+        <v>62.444</v>
+      </c>
+      <c r="F69">
+        <v>62.444</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>93.2</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>24.1</v>
+      </c>
+      <c r="K69">
+        <v>12.8</v>
+      </c>
+      <c r="L69">
+        <v>11.3</v>
+      </c>
+      <c r="M69">
+        <v>4.3835688</v>
+      </c>
+      <c r="N69">
+        <v>6.916431200000001</v>
+      </c>
+      <c r="O69">
+        <v>1.314121928</v>
+      </c>
+      <c r="P69">
+        <v>5.602309272</v>
+      </c>
+      <c r="Q69">
+        <v>18.402309272</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1644839630964847</v>
+      </c>
+      <c r="T69">
+        <v>1.978246686107757</v>
+      </c>
+      <c r="U69">
+        <v>0.0702</v>
+      </c>
+      <c r="V69">
+        <v>0.19</v>
+      </c>
+      <c r="W69">
+        <v>0.056862</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>2.577808291727964</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.09246756892776235</v>
+      </c>
+      <c r="C70">
+        <v>25.61486196748707</v>
+      </c>
+      <c r="D70">
+        <v>88.99086196748708</v>
+      </c>
+      <c r="E70">
+        <v>63.376</v>
+      </c>
+      <c r="F70">
+        <v>63.376</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>93.2</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>24.1</v>
+      </c>
+      <c r="K70">
+        <v>12.8</v>
+      </c>
+      <c r="L70">
+        <v>11.3</v>
+      </c>
+      <c r="M70">
+        <v>4.448995200000001</v>
+      </c>
+      <c r="N70">
+        <v>6.8510048</v>
+      </c>
+      <c r="O70">
+        <v>1.301690912</v>
+      </c>
+      <c r="P70">
+        <v>5.549313888</v>
+      </c>
+      <c r="Q70">
+        <v>18.349313888</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1681294028992574</v>
+      </c>
+      <c r="T70">
+        <v>2.035625360614578</v>
+      </c>
+      <c r="U70">
+        <v>0.0702</v>
+      </c>
+      <c r="V70">
+        <v>0.19</v>
+      </c>
+      <c r="W70">
+        <v>0.056862</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>2.539899346261376</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.09255789003368481</v>
+      </c>
+      <c r="C71">
+        <v>24.62379761952252</v>
+      </c>
+      <c r="D71">
+        <v>88.93179761952253</v>
+      </c>
+      <c r="E71">
+        <v>64.30800000000001</v>
+      </c>
+      <c r="F71">
+        <v>64.30800000000001</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>93.2</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>24.1</v>
+      </c>
+      <c r="K71">
+        <v>12.8</v>
+      </c>
+      <c r="L71">
+        <v>11.3</v>
+      </c>
+      <c r="M71">
+        <v>4.5144216</v>
+      </c>
+      <c r="N71">
+        <v>6.7855784</v>
+      </c>
+      <c r="O71">
+        <v>1.289259896</v>
+      </c>
+      <c r="P71">
+        <v>5.496318504</v>
+      </c>
+      <c r="Q71">
+        <v>18.296318504</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1720100323667252</v>
+      </c>
+      <c r="T71">
+        <v>2.096705885089581</v>
+      </c>
+      <c r="U71">
+        <v>0.0702</v>
+      </c>
+      <c r="V71">
+        <v>0.19</v>
+      </c>
+      <c r="W71">
+        <v>0.056862</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>2.503089210808312</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.09531311113960722</v>
+      </c>
+      <c r="C72">
+        <v>21.92698247253179</v>
+      </c>
+      <c r="D72">
+        <v>87.1669824725318</v>
+      </c>
+      <c r="E72">
+        <v>65.24000000000001</v>
+      </c>
+      <c r="F72">
+        <v>65.24000000000001</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>93.2</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>24.1</v>
+      </c>
+      <c r="K72">
+        <v>12.8</v>
+      </c>
+      <c r="L72">
+        <v>11.3</v>
+      </c>
+      <c r="M72">
+        <v>4.886476</v>
+      </c>
+      <c r="N72">
+        <v>6.413524000000001</v>
+      </c>
+      <c r="O72">
+        <v>1.21856956</v>
+      </c>
+      <c r="P72">
+        <v>5.19495444</v>
+      </c>
+      <c r="Q72">
+        <v>17.99495444</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1761493704653574</v>
+      </c>
+      <c r="T72">
+        <v>2.161858444529584</v>
+      </c>
+      <c r="U72">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V72">
+        <v>0.19</v>
+      </c>
+      <c r="W72">
+        <v>0.060669</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>2.312504962676579</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.09544150224552965</v>
+      </c>
+      <c r="C73">
+        <v>20.91444996501434</v>
+      </c>
+      <c r="D73">
+        <v>87.08644996501434</v>
+      </c>
+      <c r="E73">
+        <v>66.172</v>
+      </c>
+      <c r="F73">
+        <v>66.172</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>93.2</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>24.1</v>
+      </c>
+      <c r="K73">
+        <v>12.8</v>
+      </c>
+      <c r="L73">
+        <v>11.3</v>
+      </c>
+      <c r="M73">
+        <v>4.956282799999999</v>
+      </c>
+      <c r="N73">
+        <v>6.343717200000001</v>
+      </c>
+      <c r="O73">
+        <v>1.205306268</v>
+      </c>
+      <c r="P73">
+        <v>5.138410932000001</v>
+      </c>
+      <c r="Q73">
+        <v>17.938410932</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1805741801569988</v>
+      </c>
+      <c r="T73">
+        <v>2.231504283930966</v>
+      </c>
+      <c r="U73">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V73">
+        <v>0.19</v>
+      </c>
+      <c r="W73">
+        <v>0.060669</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>2.279934470244515</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.09556989335145208</v>
+      </c>
+      <c r="C74">
+        <v>19.90206612613848</v>
+      </c>
+      <c r="D74">
+        <v>87.00606612613848</v>
+      </c>
+      <c r="E74">
+        <v>67.104</v>
+      </c>
+      <c r="F74">
+        <v>67.104</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>93.2</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>24.1</v>
+      </c>
+      <c r="K74">
+        <v>12.8</v>
+      </c>
+      <c r="L74">
+        <v>11.3</v>
+      </c>
+      <c r="M74">
+        <v>5.0260896</v>
+      </c>
+      <c r="N74">
+        <v>6.273910400000001</v>
+      </c>
+      <c r="O74">
+        <v>1.192042976</v>
+      </c>
+      <c r="P74">
+        <v>5.081867424</v>
+      </c>
+      <c r="Q74">
+        <v>17.881867424</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1853150476837574</v>
+      </c>
+      <c r="T74">
+        <v>2.306124826146733</v>
+      </c>
+      <c r="U74">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V74">
+        <v>0.19</v>
+      </c>
+      <c r="W74">
+        <v>0.060669</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>2.248268713713341</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.09569828445737451</v>
+      </c>
+      <c r="C75">
+        <v>18.88983054460476</v>
+      </c>
+      <c r="D75">
+        <v>86.92583054460476</v>
+      </c>
+      <c r="E75">
+        <v>68.036</v>
+      </c>
+      <c r="F75">
+        <v>68.036</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>93.2</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>24.1</v>
+      </c>
+      <c r="K75">
+        <v>12.8</v>
+      </c>
+      <c r="L75">
+        <v>11.3</v>
+      </c>
+      <c r="M75">
+        <v>5.0958964</v>
+      </c>
+      <c r="N75">
+        <v>6.204103600000001</v>
+      </c>
+      <c r="O75">
+        <v>1.178779684</v>
+      </c>
+      <c r="P75">
+        <v>5.025323916000001</v>
+      </c>
+      <c r="Q75">
+        <v>17.825323916</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1904070905828685</v>
+      </c>
+      <c r="T75">
+        <v>2.386272815934039</v>
+      </c>
+      <c r="U75">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V75">
+        <v>0.19</v>
+      </c>
+      <c r="W75">
+        <v>0.060669</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>2.217470512155624</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.09582667556329694</v>
+      </c>
+      <c r="C76">
+        <v>17.87774281062957</v>
+      </c>
+      <c r="D76">
+        <v>86.84574281062957</v>
+      </c>
+      <c r="E76">
+        <v>68.968</v>
+      </c>
+      <c r="F76">
+        <v>68.968</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>93.2</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>24.1</v>
+      </c>
+      <c r="K76">
+        <v>12.8</v>
+      </c>
+      <c r="L76">
+        <v>11.3</v>
+      </c>
+      <c r="M76">
+        <v>5.1657032</v>
+      </c>
+      <c r="N76">
+        <v>6.1342968</v>
+      </c>
+      <c r="O76">
+        <v>1.165516392</v>
+      </c>
+      <c r="P76">
+        <v>4.968780408000001</v>
+      </c>
+      <c r="Q76">
+        <v>17.768780408</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1958908290896036</v>
+      </c>
+      <c r="T76">
+        <v>2.472586035704983</v>
+      </c>
+      <c r="U76">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V76">
+        <v>0.19</v>
+      </c>
+      <c r="W76">
+        <v>0.060669</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>2.187504694423791</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.09595506666921938</v>
+      </c>
+      <c r="C77">
+        <v>16.86580251593806</v>
+      </c>
+      <c r="D77">
+        <v>86.76580251593806</v>
+      </c>
+      <c r="E77">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="F77">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>93.2</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>24.1</v>
+      </c>
+      <c r="K77">
+        <v>12.8</v>
+      </c>
+      <c r="L77">
+        <v>11.3</v>
+      </c>
+      <c r="M77">
+        <v>5.23551</v>
+      </c>
+      <c r="N77">
+        <v>6.064490000000001</v>
+      </c>
+      <c r="O77">
+        <v>1.1522531</v>
+      </c>
+      <c r="P77">
+        <v>4.912236900000001</v>
+      </c>
+      <c r="Q77">
+        <v>17.7122369</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2018132666768775</v>
+      </c>
+      <c r="T77">
+        <v>2.565804313057603</v>
+      </c>
+      <c r="U77">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V77">
+        <v>0.19</v>
+      </c>
+      <c r="W77">
+        <v>0.060669</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>2.158337965164808</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.0960834577751418</v>
+      </c>
+      <c r="C78">
+        <v>15.85400925375724</v>
+      </c>
+      <c r="D78">
+        <v>86.68600925375725</v>
+      </c>
+      <c r="E78">
+        <v>70.83200000000001</v>
+      </c>
+      <c r="F78">
+        <v>70.83200000000001</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>93.2</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>24.1</v>
+      </c>
+      <c r="K78">
+        <v>12.8</v>
+      </c>
+      <c r="L78">
+        <v>11.3</v>
+      </c>
+      <c r="M78">
+        <v>5.3053168</v>
+      </c>
+      <c r="N78">
+        <v>5.994683200000001</v>
+      </c>
+      <c r="O78">
+        <v>1.138989808</v>
+      </c>
+      <c r="P78">
+        <v>4.855693392000001</v>
+      </c>
+      <c r="Q78">
+        <v>17.655693392</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2082292407297575</v>
+      </c>
+      <c r="T78">
+        <v>2.666790780189608</v>
+      </c>
+      <c r="U78">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V78">
+        <v>0.19</v>
+      </c>
+      <c r="W78">
+        <v>0.060669</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>2.129938781412639</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.09621184888106424</v>
+      </c>
+      <c r="C79">
+        <v>14.8423626188091</v>
+      </c>
+      <c r="D79">
+        <v>86.60636261880911</v>
+      </c>
+      <c r="E79">
+        <v>71.76400000000001</v>
+      </c>
+      <c r="F79">
+        <v>71.76400000000001</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>93.2</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>24.1</v>
+      </c>
+      <c r="K79">
+        <v>12.8</v>
+      </c>
+      <c r="L79">
+        <v>11.3</v>
+      </c>
+      <c r="M79">
+        <v>5.3751236</v>
+      </c>
+      <c r="N79">
+        <v>5.9248764</v>
+      </c>
+      <c r="O79">
+        <v>1.125726516</v>
+      </c>
+      <c r="P79">
+        <v>4.799149884</v>
+      </c>
+      <c r="Q79">
+        <v>17.599149884</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2152031255698445</v>
+      </c>
+      <c r="T79">
+        <v>2.776558679246135</v>
+      </c>
+      <c r="U79">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V79">
+        <v>0.19</v>
+      </c>
+      <c r="W79">
+        <v>0.060669</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>2.10227723879689</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.09634023998698665</v>
+      </c>
+      <c r="C80">
+        <v>13.83086220730374</v>
+      </c>
+      <c r="D80">
+        <v>86.52686220730374</v>
+      </c>
+      <c r="E80">
+        <v>72.696</v>
+      </c>
+      <c r="F80">
+        <v>72.696</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>93.2</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>24.1</v>
+      </c>
+      <c r="K80">
+        <v>12.8</v>
+      </c>
+      <c r="L80">
+        <v>11.3</v>
+      </c>
+      <c r="M80">
+        <v>5.4449304</v>
+      </c>
+      <c r="N80">
+        <v>5.855069600000001</v>
+      </c>
+      <c r="O80">
+        <v>1.112463224</v>
+      </c>
+      <c r="P80">
+        <v>4.742606376000001</v>
+      </c>
+      <c r="Q80">
+        <v>17.542606376</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2228109999408485</v>
+      </c>
+      <c r="T80">
+        <v>2.896305478216892</v>
+      </c>
+      <c r="U80">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V80">
+        <v>0.19</v>
+      </c>
+      <c r="W80">
+        <v>0.060669</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>2.075324966504623</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.09646863109290908</v>
+      </c>
+      <c r="C81">
+        <v>12.81950761693247</v>
+      </c>
+      <c r="D81">
+        <v>86.44750761693247</v>
+      </c>
+      <c r="E81">
+        <v>73.628</v>
+      </c>
+      <c r="F81">
+        <v>73.628</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
+        <v>93.2</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>24.1</v>
+      </c>
+      <c r="K81">
+        <v>12.8</v>
+      </c>
+      <c r="L81">
+        <v>11.3</v>
+      </c>
+      <c r="M81">
+        <v>5.5147372</v>
+      </c>
+      <c r="N81">
+        <v>5.785262800000001</v>
+      </c>
+      <c r="O81">
+        <v>1.099199932</v>
+      </c>
+      <c r="P81">
+        <v>4.686062868</v>
+      </c>
+      <c r="Q81">
+        <v>17.486062868</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2311434337757576</v>
+      </c>
+      <c r="T81">
+        <v>3.027456734232482</v>
+      </c>
+      <c r="U81">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V81">
+        <v>0.19</v>
+      </c>
+      <c r="W81">
+        <v>0.060669</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>2.049055030219754</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.09659702219883151</v>
+      </c>
+      <c r="C82">
+        <v>11.80829844686117</v>
+      </c>
+      <c r="D82">
+        <v>86.36829844686117</v>
+      </c>
+      <c r="E82">
+        <v>74.56</v>
+      </c>
+      <c r="F82">
+        <v>74.56</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>93.2</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>24.1</v>
+      </c>
+      <c r="K82">
+        <v>12.8</v>
+      </c>
+      <c r="L82">
+        <v>11.3</v>
+      </c>
+      <c r="M82">
+        <v>5.584544</v>
+      </c>
+      <c r="N82">
+        <v>5.715456000000001</v>
+      </c>
+      <c r="O82">
+        <v>1.08593664</v>
+      </c>
+      <c r="P82">
+        <v>4.629519360000001</v>
+      </c>
+      <c r="Q82">
+        <v>17.42951936</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2403091109941576</v>
+      </c>
+      <c r="T82">
+        <v>3.171723115849632</v>
+      </c>
+      <c r="U82">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V82">
+        <v>0.19</v>
+      </c>
+      <c r="W82">
+        <v>0.060669</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>2.023441842342007</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1074198433047539</v>
+      </c>
+      <c r="C83">
+        <v>4.683721610777638</v>
+      </c>
+      <c r="D83">
+        <v>80.17572161077764</v>
+      </c>
+      <c r="E83">
+        <v>75.492</v>
+      </c>
+      <c r="F83">
+        <v>75.492</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>93.2</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>24.1</v>
+      </c>
+      <c r="K83">
+        <v>12.8</v>
+      </c>
+      <c r="L83">
+        <v>11.3</v>
+      </c>
+      <c r="M83">
+        <v>6.884870400000001</v>
+      </c>
+      <c r="N83">
+        <v>4.4151296</v>
+      </c>
+      <c r="O83">
+        <v>0.838874624</v>
+      </c>
+      <c r="P83">
+        <v>3.576254976</v>
+      </c>
+      <c r="Q83">
+        <v>16.376254976</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2504395963408103</v>
+      </c>
+      <c r="T83">
+        <v>3.33117543237385</v>
+      </c>
+      <c r="U83">
+        <v>0.0912</v>
+      </c>
+      <c r="V83">
+        <v>0.19</v>
+      </c>
+      <c r="W83">
+        <v>0.07387200000000001</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>1.641279986911591</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1076802644106764</v>
+      </c>
+      <c r="C84">
+        <v>3.613636454893054</v>
+      </c>
+      <c r="D84">
+        <v>80.03763645489306</v>
+      </c>
+      <c r="E84">
+        <v>76.42400000000001</v>
+      </c>
+      <c r="F84">
+        <v>76.42400000000001</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>93.2</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>24.1</v>
+      </c>
+      <c r="K84">
+        <v>12.8</v>
+      </c>
+      <c r="L84">
+        <v>11.3</v>
+      </c>
+      <c r="M84">
+        <v>6.9698688</v>
+      </c>
+      <c r="N84">
+        <v>4.3301312</v>
+      </c>
+      <c r="O84">
+        <v>0.8227249280000001</v>
+      </c>
+      <c r="P84">
+        <v>3.507406272</v>
+      </c>
+      <c r="Q84">
+        <v>16.307406272</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2616956911704243</v>
+      </c>
+      <c r="T84">
+        <v>3.508344672956315</v>
+      </c>
+      <c r="U84">
+        <v>0.0912</v>
+      </c>
+      <c r="V84">
+        <v>0.19</v>
+      </c>
+      <c r="W84">
+        <v>0.07387200000000001</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>1.621264377315108</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1079406855165988</v>
+      </c>
+      <c r="C85">
+        <v>2.544026124223294</v>
+      </c>
+      <c r="D85">
+        <v>79.9000261242233</v>
+      </c>
+      <c r="E85">
+        <v>77.35600000000001</v>
+      </c>
+      <c r="F85">
+        <v>77.35600000000001</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>93.2</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>24.1</v>
+      </c>
+      <c r="K85">
+        <v>12.8</v>
+      </c>
+      <c r="L85">
+        <v>11.3</v>
+      </c>
+      <c r="M85">
+        <v>7.054867200000001</v>
+      </c>
+      <c r="N85">
+        <v>4.245132799999999</v>
+      </c>
+      <c r="O85">
+        <v>0.8065752319999999</v>
+      </c>
+      <c r="P85">
+        <v>3.438557567999999</v>
+      </c>
+      <c r="Q85">
+        <v>16.238557568</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2742760324505813</v>
+      </c>
+      <c r="T85">
+        <v>3.706357353607305</v>
+      </c>
+      <c r="U85">
+        <v>0.0912</v>
+      </c>
+      <c r="V85">
+        <v>0.19</v>
+      </c>
+      <c r="W85">
+        <v>0.07387200000000001</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>1.601731071564323</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.1082011066225212</v>
+      </c>
+      <c r="C86">
+        <v>1.474888173842118</v>
+      </c>
+      <c r="D86">
+        <v>79.76288817384211</v>
+      </c>
+      <c r="E86">
+        <v>78.288</v>
+      </c>
+      <c r="F86">
+        <v>78.288</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>93.2</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>24.1</v>
+      </c>
+      <c r="K86">
+        <v>12.8</v>
+      </c>
+      <c r="L86">
+        <v>11.3</v>
+      </c>
+      <c r="M86">
+        <v>7.1398656</v>
+      </c>
+      <c r="N86">
+        <v>4.1601344</v>
+      </c>
+      <c r="O86">
+        <v>0.7904255360000001</v>
+      </c>
+      <c r="P86">
+        <v>3.369708864000001</v>
+      </c>
+      <c r="Q86">
+        <v>16.169708864</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.2884289163907577</v>
+      </c>
+      <c r="T86">
+        <v>3.929121619339667</v>
+      </c>
+      <c r="U86">
+        <v>0.0912</v>
+      </c>
+      <c r="V86">
+        <v>0.19</v>
+      </c>
+      <c r="W86">
+        <v>0.07387200000000001</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>1.582662844521891</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1084615277284437</v>
+      </c>
+      <c r="C87">
+        <v>0.4062201755801169</v>
+      </c>
+      <c r="D87">
+        <v>79.62622017558012</v>
+      </c>
+      <c r="E87">
+        <v>79.22</v>
+      </c>
+      <c r="F87">
+        <v>79.22</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>93.2</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>24.1</v>
+      </c>
+      <c r="K87">
+        <v>12.8</v>
+      </c>
+      <c r="L87">
+        <v>11.3</v>
+      </c>
+      <c r="M87">
+        <v>7.224864</v>
+      </c>
+      <c r="N87">
+        <v>4.075136000000001</v>
+      </c>
+      <c r="O87">
+        <v>0.7742758400000002</v>
+      </c>
+      <c r="P87">
+        <v>3.30086016</v>
+      </c>
+      <c r="Q87">
+        <v>16.10086016</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3044688515229577</v>
+      </c>
+      <c r="T87">
+        <v>4.181587787169679</v>
+      </c>
+      <c r="U87">
+        <v>0.0912</v>
+      </c>
+      <c r="V87">
+        <v>0.19</v>
+      </c>
+      <c r="W87">
+        <v>0.07387200000000001</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>1.564043281645163</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1087219488343661</v>
+      </c>
+      <c r="C88">
+        <v>-0.6619802821186056</v>
+      </c>
+      <c r="D88">
+        <v>79.4900197178814</v>
+      </c>
+      <c r="E88">
+        <v>80.152</v>
+      </c>
+      <c r="F88">
+        <v>80.152</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>93.2</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>24.1</v>
+      </c>
+      <c r="K88">
+        <v>12.8</v>
+      </c>
+      <c r="L88">
+        <v>11.3</v>
+      </c>
+      <c r="M88">
+        <v>7.3098624</v>
+      </c>
+      <c r="N88">
+        <v>3.990137600000001</v>
+      </c>
+      <c r="O88">
+        <v>0.7581261440000001</v>
+      </c>
+      <c r="P88">
+        <v>3.232011456</v>
+      </c>
+      <c r="Q88">
+        <v>16.032011456</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3228002059597578</v>
+      </c>
+      <c r="T88">
+        <v>4.470120550403979</v>
+      </c>
+      <c r="U88">
+        <v>0.0912</v>
+      </c>
+      <c r="V88">
+        <v>0.19</v>
+      </c>
+      <c r="W88">
+        <v>0.07387200000000001</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>1.545856731858592</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1089823699402885</v>
+      </c>
+      <c r="C89">
+        <v>-1.729715594338302</v>
+      </c>
+      <c r="D89">
+        <v>79.3542844056617</v>
+      </c>
+      <c r="E89">
+        <v>81.084</v>
+      </c>
+      <c r="F89">
+        <v>81.084</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>93.2</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>24.1</v>
+      </c>
+      <c r="K89">
+        <v>12.8</v>
+      </c>
+      <c r="L89">
+        <v>11.3</v>
+      </c>
+      <c r="M89">
+        <v>7.394860800000001</v>
+      </c>
+      <c r="N89">
+        <v>3.9051392</v>
+      </c>
+      <c r="O89">
+        <v>0.741976448</v>
+      </c>
+      <c r="P89">
+        <v>3.163162752</v>
+      </c>
+      <c r="Q89">
+        <v>15.963162752</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3439517687714502</v>
+      </c>
+      <c r="T89">
+        <v>4.803042969520478</v>
+      </c>
+      <c r="U89">
+        <v>0.0912</v>
+      </c>
+      <c r="V89">
+        <v>0.19</v>
+      </c>
+      <c r="W89">
+        <v>0.07387200000000001</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>1.528088263676309</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.109242791046211</v>
+      </c>
+      <c r="C90">
+        <v>-2.79698813983191</v>
+      </c>
+      <c r="D90">
+        <v>79.2190118601681</v>
+      </c>
+      <c r="E90">
+        <v>82.01600000000001</v>
+      </c>
+      <c r="F90">
+        <v>82.01600000000001</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>93.2</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>24.1</v>
+      </c>
+      <c r="K90">
+        <v>12.8</v>
+      </c>
+      <c r="L90">
+        <v>11.3</v>
+      </c>
+      <c r="M90">
+        <v>7.479859200000001</v>
+      </c>
+      <c r="N90">
+        <v>3.8201408</v>
+      </c>
+      <c r="O90">
+        <v>0.725826752</v>
+      </c>
+      <c r="P90">
+        <v>3.094314048</v>
+      </c>
+      <c r="Q90">
+        <v>15.894314048</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.368628592051758</v>
+      </c>
+      <c r="T90">
+        <v>5.191452458489728</v>
+      </c>
+      <c r="U90">
+        <v>0.0912</v>
+      </c>
+      <c r="V90">
+        <v>0.19</v>
+      </c>
+      <c r="W90">
+        <v>0.07387200000000001</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>1.510723624316351</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.1611400292383557</v>
+      </c>
+      <c r="C91">
+        <v>-23.81650346539539</v>
+      </c>
+      <c r="D91">
+        <v>59.13149653460462</v>
+      </c>
+      <c r="E91">
+        <v>82.94800000000001</v>
+      </c>
+      <c r="F91">
+        <v>82.94800000000001</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>93.2</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>24.1</v>
+      </c>
+      <c r="K91">
+        <v>12.8</v>
+      </c>
+      <c r="L91">
+        <v>11.3</v>
+      </c>
+      <c r="M91">
+        <v>12.9896568</v>
+      </c>
+      <c r="N91">
+        <v>-1.689656800000002</v>
+      </c>
+      <c r="O91">
+        <v>-0.3210347920000003</v>
+      </c>
+      <c r="P91">
+        <v>-1.368622008000001</v>
+      </c>
+      <c r="Q91">
+        <v>11.431377992</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4072955447731905</v>
+      </c>
+      <c r="T91">
+        <v>5.800064481841804</v>
+      </c>
+      <c r="U91">
+        <v>0.1566</v>
+      </c>
+      <c r="V91">
+        <v>0.165285352265812</v>
+      </c>
+      <c r="W91">
+        <v>0.1307163138351738</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.8699229066621682</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.1623180292383557</v>
+      </c>
+      <c r="C92">
+        <v>-25.08689868062906</v>
+      </c>
+      <c r="D92">
+        <v>58.79310131937095</v>
+      </c>
+      <c r="E92">
+        <v>83.88000000000001</v>
+      </c>
+      <c r="F92">
+        <v>83.88000000000001</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <v>93.2</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>24.1</v>
+      </c>
+      <c r="K92">
+        <v>12.8</v>
+      </c>
+      <c r="L92">
+        <v>11.3</v>
+      </c>
+      <c r="M92">
+        <v>13.135608</v>
+      </c>
+      <c r="N92">
+        <v>-1.835608000000002</v>
+      </c>
+      <c r="O92">
+        <v>-0.3487655200000004</v>
+      </c>
+      <c r="P92">
+        <v>-1.486842480000002</v>
+      </c>
+      <c r="Q92">
+        <v>11.31315752</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4441450992505097</v>
+      </c>
+      <c r="T92">
+        <v>6.380070930025986</v>
+      </c>
+      <c r="U92">
+        <v>0.1566</v>
+      </c>
+      <c r="V92">
+        <v>0.1634488483517474</v>
+      </c>
+      <c r="W92">
+        <v>0.1310039103481164</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.8602570965881441</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.1634960292383557</v>
+      </c>
+      <c r="C93">
+        <v>-26.3534428270841</v>
+      </c>
+      <c r="D93">
+        <v>58.45855717291591</v>
+      </c>
+      <c r="E93">
+        <v>84.81200000000001</v>
+      </c>
+      <c r="F93">
+        <v>84.81200000000001</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>93.2</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>24.1</v>
+      </c>
+      <c r="K93">
+        <v>12.8</v>
+      </c>
+      <c r="L93">
+        <v>11.3</v>
+      </c>
+      <c r="M93">
+        <v>13.2815592</v>
+      </c>
+      <c r="N93">
+        <v>-1.981559200000003</v>
+      </c>
+      <c r="O93">
+        <v>-0.3764962480000006</v>
+      </c>
+      <c r="P93">
+        <v>-1.605062952000003</v>
+      </c>
+      <c r="Q93">
+        <v>11.194937048</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.4891834436116773</v>
+      </c>
+      <c r="T93">
+        <v>7.088967700028872</v>
+      </c>
+      <c r="U93">
+        <v>0.1566</v>
+      </c>
+      <c r="V93">
+        <v>0.1616527071610688</v>
+      </c>
+      <c r="W93">
+        <v>0.1312851860585766</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.8508037219003622</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.1646740292383557</v>
+      </c>
+      <c r="C94">
+        <v>-27.61620127278795</v>
+      </c>
+      <c r="D94">
+        <v>58.12779872721205</v>
+      </c>
+      <c r="E94">
+        <v>85.744</v>
+      </c>
+      <c r="F94">
+        <v>85.744</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>93.2</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>24.1</v>
+      </c>
+      <c r="K94">
+        <v>12.8</v>
+      </c>
+      <c r="L94">
+        <v>11.3</v>
+      </c>
+      <c r="M94">
+        <v>13.4275104</v>
+      </c>
+      <c r="N94">
+        <v>-2.1275104</v>
+      </c>
+      <c r="O94">
+        <v>-0.4042269760000001</v>
+      </c>
+      <c r="P94">
+        <v>-1.723283424</v>
+      </c>
+      <c r="Q94">
+        <v>11.076716576</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.545481374063137</v>
+      </c>
+      <c r="T94">
+        <v>7.975088662532483</v>
+      </c>
+      <c r="U94">
+        <v>0.1566</v>
+      </c>
+      <c r="V94">
+        <v>0.1598956125180138</v>
+      </c>
+      <c r="W94">
+        <v>0.1315603470796791</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.8415558553579672</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.1658520292383557</v>
+      </c>
+      <c r="C95">
+        <v>-28.87523791468265</v>
+      </c>
+      <c r="D95">
+        <v>57.80076208531735</v>
+      </c>
+      <c r="E95">
+        <v>86.676</v>
+      </c>
+      <c r="F95">
+        <v>86.676</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <v>93.2</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>24.1</v>
+      </c>
+      <c r="K95">
+        <v>12.8</v>
+      </c>
+      <c r="L95">
+        <v>11.3</v>
+      </c>
+      <c r="M95">
+        <v>13.5734616</v>
+      </c>
+      <c r="N95">
+        <v>-2.273461600000001</v>
+      </c>
+      <c r="O95">
+        <v>-0.4319577040000002</v>
+      </c>
+      <c r="P95">
+        <v>-1.841503896000001</v>
+      </c>
+      <c r="Q95">
+        <v>10.958496104</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.6178644275007283</v>
+      </c>
+      <c r="T95">
+        <v>9.11438704289427</v>
+      </c>
+      <c r="U95">
+        <v>0.1566</v>
+      </c>
+      <c r="V95">
+        <v>0.1581763048565297</v>
+      </c>
+      <c r="W95">
+        <v>0.1318295906594675</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.8325068676659459</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.1670300292383557</v>
+      </c>
+      <c r="C96">
+        <v>-30.13061521977597</v>
+      </c>
+      <c r="D96">
+        <v>57.47738478022404</v>
+      </c>
+      <c r="E96">
+        <v>87.608</v>
+      </c>
+      <c r="F96">
+        <v>87.608</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>93.2</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>24.1</v>
+      </c>
+      <c r="K96">
+        <v>12.8</v>
+      </c>
+      <c r="L96">
+        <v>11.3</v>
+      </c>
+      <c r="M96">
+        <v>13.7194128</v>
+      </c>
+      <c r="N96">
+        <v>-2.419412800000002</v>
+      </c>
+      <c r="O96">
+        <v>-0.4596884320000003</v>
+      </c>
+      <c r="P96">
+        <v>-1.959724368000001</v>
+      </c>
+      <c r="Q96">
+        <v>10.840275632</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.7143751654175163</v>
+      </c>
+      <c r="T96">
+        <v>10.63345155004331</v>
+      </c>
+      <c r="U96">
+        <v>0.1566</v>
+      </c>
+      <c r="V96">
+        <v>0.1564935782091199</v>
+      </c>
+      <c r="W96">
+        <v>0.1320931056524518</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.8236504116269465</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.1682080292383557</v>
+      </c>
+      <c r="C97">
+        <v>-31.38239426491928</v>
+      </c>
+      <c r="D97">
+        <v>57.15760573508073</v>
+      </c>
+      <c r="E97">
+        <v>88.54000000000001</v>
+      </c>
+      <c r="F97">
+        <v>88.54000000000001</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>93.2</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>24.1</v>
+      </c>
+      <c r="K97">
+        <v>12.8</v>
+      </c>
+      <c r="L97">
+        <v>11.3</v>
+      </c>
+      <c r="M97">
+        <v>13.865364</v>
+      </c>
+      <c r="N97">
+        <v>-2.565364000000002</v>
+      </c>
+      <c r="O97">
+        <v>-0.4874191600000005</v>
+      </c>
+      <c r="P97">
+        <v>-2.077944840000002</v>
+      </c>
+      <c r="Q97">
+        <v>10.72205516</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.8494901985010204</v>
+      </c>
+      <c r="T97">
+        <v>12.76014186005199</v>
+      </c>
+      <c r="U97">
+        <v>0.1566</v>
+      </c>
+      <c r="V97">
+        <v>0.1548462773858659</v>
+      </c>
+      <c r="W97">
+        <v>0.1323510729613734</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.8149804072940312</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.1693860292383557</v>
+      </c>
+      <c r="C98">
+        <v>-32.63063477526448</v>
+      </c>
+      <c r="D98">
+        <v>56.84136522473552</v>
+      </c>
+      <c r="E98">
+        <v>89.47199999999999</v>
+      </c>
+      <c r="F98">
+        <v>89.47199999999999</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>93.2</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>24.1</v>
+      </c>
+      <c r="K98">
+        <v>12.8</v>
+      </c>
+      <c r="L98">
+        <v>11.3</v>
+      </c>
+      <c r="M98">
+        <v>14.0113152</v>
+      </c>
+      <c r="N98">
+        <v>-2.7113152</v>
+      </c>
+      <c r="O98">
+        <v>-0.5151498879999999</v>
+      </c>
+      <c r="P98">
+        <v>-2.196165312</v>
+      </c>
+      <c r="Q98">
+        <v>10.603834688</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.052162748126273</v>
+      </c>
+      <c r="T98">
+        <v>15.95017732506494</v>
+      </c>
+      <c r="U98">
+        <v>0.1566</v>
+      </c>
+      <c r="V98">
+        <v>0.1532332953297632</v>
+      </c>
+      <c r="W98">
+        <v>0.1326036659513591</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.8064910280513853</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2229458351883522</v>
+      </c>
+      <c r="C99">
+        <v>-44.98749485319603</v>
+      </c>
+      <c r="D99">
+        <v>45.41650514680397</v>
+      </c>
+      <c r="E99">
+        <v>90.404</v>
+      </c>
+      <c r="F99">
+        <v>90.404</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
+      </c>
+      <c r="H99">
+        <v>93.2</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>24.1</v>
+      </c>
+      <c r="K99">
+        <v>12.8</v>
+      </c>
+      <c r="L99">
+        <v>11.3</v>
+      </c>
+      <c r="M99">
+        <v>18.8763552</v>
+      </c>
+      <c r="N99">
+        <v>-7.576355199999998</v>
+      </c>
+      <c r="O99">
+        <v>-1.439507488</v>
+      </c>
+      <c r="P99">
+        <v>-6.136847711999999</v>
+      </c>
+      <c r="Q99">
+        <v>6.663152288000002</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.448210529168249</v>
+      </c>
+      <c r="T99">
+        <v>22.18390986407758</v>
+      </c>
+      <c r="U99">
+        <v>0.2088</v>
+      </c>
+      <c r="V99">
+        <v>0.1137401779767315</v>
+      </c>
+      <c r="W99">
+        <v>0.1850510508384585</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.5986325156670076</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2246458351883522</v>
+      </c>
+      <c r="C100">
+        <v>-46.20739917541649</v>
+      </c>
+      <c r="D100">
+        <v>45.12860082458351</v>
+      </c>
+      <c r="E100">
+        <v>91.336</v>
+      </c>
+      <c r="F100">
+        <v>91.336</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
+      </c>
+      <c r="H100">
+        <v>93.2</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>24.1</v>
+      </c>
+      <c r="K100">
+        <v>12.8</v>
+      </c>
+      <c r="L100">
+        <v>11.3</v>
+      </c>
+      <c r="M100">
+        <v>19.0709568</v>
+      </c>
+      <c r="N100">
+        <v>-7.7709568</v>
+      </c>
+      <c r="O100">
+        <v>-1.476481792</v>
+      </c>
+      <c r="P100">
+        <v>-6.294475008</v>
+      </c>
+      <c r="Q100">
+        <v>6.505524992000001</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.152915793752373</v>
+      </c>
+      <c r="T100">
+        <v>33.27586479611637</v>
+      </c>
+      <c r="U100">
+        <v>0.2088</v>
+      </c>
+      <c r="V100">
+        <v>0.1125795639157444</v>
+      </c>
+      <c r="W100">
+        <v>0.1852933870543926</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.592524020609181</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2263458351883522</v>
+      </c>
+      <c r="C101">
+        <v>-47.42367632469166</v>
+      </c>
+      <c r="D101">
+        <v>44.84432367530834</v>
+      </c>
+      <c r="E101">
+        <v>92.268</v>
+      </c>
+      <c r="F101">
+        <v>92.268</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <v>93.2</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>24.1</v>
+      </c>
+      <c r="K101">
+        <v>12.8</v>
+      </c>
+      <c r="L101">
+        <v>11.3</v>
+      </c>
+      <c r="M101">
+        <v>19.2655584</v>
+      </c>
+      <c r="N101">
+        <v>-7.965558399999999</v>
+      </c>
+      <c r="O101">
+        <v>-1.513456096</v>
+      </c>
+      <c r="P101">
+        <v>-6.452102303999999</v>
+      </c>
+      <c r="Q101">
+        <v>6.347897696000001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.267031587504747</v>
+      </c>
+      <c r="T101">
+        <v>66.55172959223275</v>
+      </c>
+      <c r="U101">
+        <v>0.2088</v>
+      </c>
+      <c r="V101">
+        <v>0.1114423966034641</v>
+      </c>
+      <c r="W101">
+        <v>0.1855308275891967</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.5865389294919165</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
